--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.46</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1348,10 +1348,10 @@
         <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
         <v>2.62</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
         <v>3.95</v>
@@ -984,7 +984,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I5" t="n">
         <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 10:30:55</t>
+          <t>2026-03-25 12:35:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
         <v>2.24</v>
@@ -960,13 +960,13 @@
         <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 12:35:31</t>
+          <t>2026-03-25 14:40:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,378 +1131,2318 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 14:40:01</t>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Danish 2nd Division</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FC Helsingor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vendsyssel FF</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sochaux</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quevilly Rouen</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aubagne FC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Versailles 78 FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Orleans</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Villefranche Beaujolais</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chateauroux</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Concarneau</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Boca Juniors de Cali</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F15" t="n">
         <v>3.3</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G15" t="n">
         <v>3.7</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H15" t="n">
         <v>2.3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I15" t="n">
         <v>2.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J15" t="n">
         <v>3.2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K15" t="n">
         <v>3.55</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q15" t="n">
         <v>2.38</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-25 14:40:01</t>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:45:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,33 +743,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fremad Amager</t>
+          <t>FK Puchov</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thisted</t>
+          <t>Triglav</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Rudar</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -957,7 +957,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Roskilde</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -1330,16 +1330,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1372,13 +1372,13 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,72 +1713,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1847,10 +1847,10 @@
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -1859,10 +1859,10 @@
         <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.03</v>
@@ -1883,21 +1883,21 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
         <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,23 +1945,23 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.23</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T8" t="n">
         <v>1.01</v>
       </c>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>1.18</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,184 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
@@ -2494,55 +2494,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H12" t="n">
         <v>5.3</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.94</v>
-      </c>
       <c r="I12" t="n">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,378 +3071,2900 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 16:45:16</t>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aubagne FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Raith</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ayr</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Partick</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ross Co</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inverness CT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Queen of South</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X22" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Welsh Premiership</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Caernarfon Town</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The New Saints</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X23" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Boca Juniors de Cali</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K25" t="n">
+        <v>950</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F28" t="n">
         <v>3.3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G28" t="n">
         <v>3.7</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H28" t="n">
         <v>2.3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I28" t="n">
         <v>2.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J28" t="n">
         <v>3.2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K28" t="n">
         <v>3.55</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L28" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P28" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q28" t="n">
         <v>2.38</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S28" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U28" t="n">
         <v>0</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V28" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W28" t="n">
         <v>0</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X28" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y28" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z28" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA28" t="n">
         <v>0</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD28" t="n">
         <v>0</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE28" t="n">
         <v>0</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG28" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH28" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI28" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ28" t="n">
         <v>0</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK28" t="n">
         <v>0</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL28" t="n">
         <v>0</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AM28" t="n">
         <v>0</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN28" t="n">
         <v>0</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO28" t="n">
         <v>0</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP28" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ28" t="n">
         <v>0</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR28" t="n">
         <v>0</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AS28" t="n">
         <v>0</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AU28" t="n">
         <v>0</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AV28" t="n">
         <v>0</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AW28" t="n">
         <v>0</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AX28" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AY28" t="n">
         <v>0</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="AZ28" t="n">
         <v>0</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BA28" t="n">
         <v>0</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB28" t="n">
         <v>0</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BC28" t="n">
         <v>0</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BD28" t="n">
         <v>0</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BE28" t="n">
         <v>0</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BF28" t="n">
         <v>0</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BG28" t="n">
         <v>0</v>
       </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-25 16:45:16</t>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:52:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
         <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q4" t="n">
         <v>1.02</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1948,19 +1948,19 @@
         <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2333,28 +2333,28 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.19</v>
@@ -2366,16 +2366,16 @@
         <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
         <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>9.4</v>
@@ -2387,22 +2387,22 @@
         <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
@@ -2414,43 +2414,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
         <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2459,10 +2459,10 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P11" t="n">
         <v>1.86</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2724,10 +2724,10 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
         <v>2.14</v>
@@ -2736,7 +2736,7 @@
         <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
         <v>2.02</v>
@@ -2745,7 +2745,7 @@
         <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>2.18</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.91</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>5.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -3515,22 +3515,22 @@
         <v>3.3</v>
       </c>
       <c r="T16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.65</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>17</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
         <v>29</v>
@@ -3545,7 +3545,7 @@
         <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>48</v>
@@ -3554,7 +3554,7 @@
         <v>17</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
@@ -3563,10 +3563,10 @@
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
         <v>44</v>
@@ -3587,22 +3587,22 @@
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="AV16" t="n">
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -3611,32 +3611,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB16" t="n">
         <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3718,7 +3718,7 @@
         <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
         <v>1.47</v>
@@ -4088,13 +4088,13 @@
         <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
         <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
         <v>2.64</v>
@@ -4276,7 +4276,7 @@
         <v>1.61</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P20" t="n">
         <v>1.6</v>
@@ -4315,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>17</v>
@@ -4342,7 +4342,7 @@
         <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4360,7 +4360,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
         <v>14.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4464,10 +4464,10 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
@@ -4479,16 +4479,16 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="V21" t="n">
         <v>1.22</v>
@@ -4497,116 +4497,116 @@
         <v>2.04</v>
       </c>
       <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AW21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10</v>
       </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>2.72</v>
-      </c>
       <c r="BG21" t="n">
-        <v>2.72</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4643,25 +4643,25 @@
         <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
         <v>1.24</v>
@@ -4670,19 +4670,19 @@
         <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>1.13</v>
@@ -4691,7 +4691,7 @@
         <v>2.58</v>
       </c>
       <c r="X22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
         <v>1000</v>
@@ -4748,59 +4748,59 @@
         <v>1.68</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AT22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BC22" t="n">
         <v>1.56</v>
       </c>
-      <c r="AU22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BD22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
         <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
         <v>5.3</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G24" t="n">
         <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I24" t="n">
         <v>2.26</v>
@@ -5040,7 +5040,7 @@
         <v>2.96</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>85</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,22 +5049,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
         <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>2.9</v>
       </c>
       <c r="H25" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I25" t="n">
         <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,7 +5267,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
         <v>1.53</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -5431,16 +5431,16 @@
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
         <v>1.53</v>
@@ -5449,16 +5449,16 @@
         <v>2.66</v>
       </c>
       <c r="R26" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5467,116 +5467,116 @@
         <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI26" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.3</v>
+        <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB26" t="n">
         <v>9</v>
       </c>
-      <c r="AY26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>20</v>
-      </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.7</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -5625,13 +5625,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>1.48</v>
@@ -5643,7 +5643,7 @@
         <v>1.48</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
         <v>1.48</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,201 +5770,395 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Paysandu FC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:57:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>3.3</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G29" t="n">
         <v>3.7</v>
       </c>
-      <c r="H28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I29" t="n">
         <v>2.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29" t="n">
         <v>3.55</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="L29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2.38</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-25 18:52:04</t>
+      <c r="R29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -760,19 +760,19 @@
         <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -808,7 +808,7 @@
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.02</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
         <v>1.71</v>
@@ -2745,7 +2745,7 @@
         <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>2.18</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.91</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H15" t="n">
         <v>4.2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
         <v>2.46</v>
@@ -3482,7 +3482,7 @@
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -3515,22 +3515,22 @@
         <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X16" t="n">
         <v>17</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
         <v>29</v>
@@ -3587,56 +3587,56 @@
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
         <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AV16" t="n">
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB16" t="n">
         <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.84</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -5028,19 +5028,19 @@
         <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="I24" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>2.96</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5064,7 +5064,7 @@
         <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>2.9</v>
       </c>
       <c r="H25" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="I25" t="n">
         <v>4.6</v>
@@ -5234,7 +5234,7 @@
         <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5246,19 +5246,19 @@
         <v>1.46</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P25" t="n">
         <v>1.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>
@@ -6013,31 +6013,31 @@
         <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
         <v>1.62</v>
       </c>
       <c r="O29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
         <v>2.38</v>
       </c>
       <c r="R29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
         <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U29" t="n">
         <v>1.57</v>
@@ -6049,7 +6049,7 @@
         <v>1.37</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
         <v>11</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.99</v>
+        <v>9.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="AX29" t="n">
-        <v>15.5</v>
+        <v>2.44</v>
       </c>
       <c r="AY29" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 20:57:51</t>
+          <t>2026-03-25 23:03:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,7 +784,7 @@
         <v>2.04</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.04</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fremad Amager</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thisted</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Roskilde</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1539,7 +1539,7 @@
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H7" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NK Brinje Grosuplje</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1927,13 +1927,13 @@
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NK Slovenska Bistrica</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2127,7 +2127,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1.21</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="G11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="G12" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="H13" t="n">
-        <v>2.66</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2918,143 +2918,143 @@
         <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
         <v>1.71</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W13" t="n">
         <v>2.18</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -3076,67 +3076,67 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I14" t="n">
         <v>6.8</v>
       </c>
-      <c r="I14" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3154,7 +3154,7 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.34</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -3270,55 +3270,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.31</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.14</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" t="n">
         <v>17</v>
       </c>
-      <c r="Y16" t="n">
-        <v>16</v>
-      </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO16" t="n">
         <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>46</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.84</v>
+        <v>4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX17" t="n">
         <v>5.3</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="AY17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" t="n">
         <v>5.7</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,67 +3852,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.76</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>2.56</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3951,10 +3951,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,69 +3969,69 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,76 +4079,76 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S19" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>1.6</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>44</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC19" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG19" t="n">
         <v>17</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4163,69 +4163,69 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.04</v>
+        <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV19" t="n">
-        <v>2.04</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.04</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
         <v>3.25</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF20" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.79</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>2.26</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>1.76</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>1.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,67 +4628,67 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="G22" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,10 +4715,10 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4727,10 +4727,10 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4745,69 +4745,69 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.49</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.49</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="G23" t="n">
-        <v>5.8</v>
+        <v>1.45</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.86</v>
+        <v>15.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="V23" t="n">
-        <v>2.16</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="X23" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AE23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>120</v>
+        <v>11.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
         <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="AO23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG23" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
         <v>1.46</v>
       </c>
       <c r="O25" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P25" t="n">
         <v>1.46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,395 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 23:03:09</t>
+          <t>2026-03-26 01:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brazilian Campeonato Women</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sao Paulo (W)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Palmeiras (W)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-26 01:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:10:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-26 01:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -760,109 +760,109 @@
         <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
         <v>5.5</v>
@@ -1745,7 +1745,7 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1757,7 +1757,7 @@
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
         <v>1.81</v>
@@ -1769,7 +1769,7 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
         <v>2.1</v>
@@ -1790,10 +1790,10 @@
         <v>46</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
         <v>9.4</v>
@@ -1802,7 +1802,7 @@
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
         <v>10.5</v>
@@ -1811,10 +1811,10 @@
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
         <v>18</v>
@@ -1823,7 +1823,7 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1832,19 +1832,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -1859,7 +1859,7 @@
         <v>55</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
@@ -1877,7 +1877,7 @@
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE7" t="n">
         <v>11.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>1.34</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2333,13 +2333,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2503,43 +2503,43 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
         <v>3.85</v>
@@ -2548,13 +2548,13 @@
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.49</v>
+        <v>1.99</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.49</v>
+        <v>1.99</v>
       </c>
       <c r="BB11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BE11" t="n">
         <v>2</v>
       </c>
-      <c r="BE11" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>1.91</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
@@ -2712,7 +2712,7 @@
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
         <v>5.3</v>
@@ -2909,19 +2909,19 @@
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
         <v>2.14</v>
@@ -2930,25 +2930,25 @@
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
         <v>55</v>
@@ -2960,10 +2960,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2975,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,10 +3005,10 @@
         <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3017,13 +3017,13 @@
         <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
@@ -3032,29 +3032,29 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
         <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG13" t="n">
         <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
         <v>1.86</v>
@@ -3121,22 +3121,22 @@
         <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.03</v>
@@ -3205,10 +3205,10 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
         <v>1.03</v>
@@ -3217,10 +3217,10 @@
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.03</v>
@@ -3241,14 +3241,14 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I15" t="n">
         <v>3.1</v>
@@ -3297,22 +3297,22 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
         <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.27</v>
@@ -3321,22 +3321,22 @@
         <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
         <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,13 +3345,13 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
@@ -3360,7 +3360,7 @@
         <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -3387,37 +3387,37 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
         <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
         <v>1.03</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.5</v>
@@ -3503,7 +3503,7 @@
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3518,13 +3518,13 @@
         <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
         <v>14</v>
@@ -3569,7 +3569,7 @@
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3587,7 +3587,7 @@
         <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS16" t="n">
         <v>8.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G17" t="n">
         <v>5.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -3718,10 +3718,10 @@
         <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
@@ -3733,7 +3733,7 @@
         <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -3745,10 +3745,10 @@
         <v>970</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
@@ -3769,25 +3769,25 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ17" t="n">
         <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
@@ -3796,41 +3796,41 @@
         <v>8.4</v>
       </c>
       <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY17" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
         <v>5.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G18" t="n">
         <v>1.58</v>
@@ -3888,7 +3888,7 @@
         <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
         <v>2.02</v>
@@ -3951,10 +3951,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.68</v>
+        <v>2.66</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.51</v>
+        <v>3.65</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.49</v>
+        <v>3.55</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.49</v>
+        <v>3.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.68</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.68</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.55</v>
+        <v>3.95</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.56</v>
+        <v>4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.68</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.68</v>
+        <v>3.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I19" t="n">
         <v>3.75</v>
@@ -4076,149 +4076,149 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
         <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.83</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.67</v>
       </c>
       <c r="V19" t="n">
         <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>13</v>
       </c>
-      <c r="Y19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY19" t="n">
         <v>10</v>
       </c>
-      <c r="AD19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AZ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG19" t="n">
         <v>50</v>
       </c>
-      <c r="AK19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4252,61 +4252,61 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
         <v>3.85</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
       </c>
       <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
         <v>29</v>
@@ -4318,7 +4318,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>17</v>
@@ -4327,7 +4327,7 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -4339,10 +4339,10 @@
         <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
         <v>44</v>
@@ -4351,7 +4351,7 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
         <v>46</v>
@@ -4360,7 +4360,7 @@
         <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>4.4</v>
@@ -4372,16 +4372,16 @@
         <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>8.6</v>
@@ -4390,29 +4390,29 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC20" t="n">
         <v>4.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
         <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4443,145 +4443,145 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="G21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.3</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.76</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
         <v>1.03</v>
@@ -4599,14 +4599,14 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4831,28 +4831,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="G23" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H23" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
         <v>3.9</v>
@@ -4864,7 +4864,7 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R23" t="n">
         <v>1.38</v>
@@ -4873,22 +4873,22 @@
         <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4903,7 +4903,7 @@
         <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4912,19 +4912,19 @@
         <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>60</v>
@@ -4945,56 +4945,56 @@
         <v>23</v>
       </c>
       <c r="AR23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS23" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS23" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AT23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>24</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H24" t="n">
         <v>1.94</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J24" t="n">
         <v>2.96</v>
@@ -5043,37 +5043,37 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="W24" t="n">
         <v>1.21</v>
@@ -5148,7 +5148,7 @@
         <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV24" t="n">
         <v>1.03</v>
@@ -5184,11 +5184,11 @@
         <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5219,112 +5219,112 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="G25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J25" t="n">
         <v>2.9</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.78</v>
-      </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="O25" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP25" t="n">
         <v>1.03</v>
@@ -5375,14 +5375,14 @@
         <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5425,40 +5425,40 @@
         <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
         <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5467,7 +5467,7 @@
         <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y26" t="n">
         <v>11.5</v>
@@ -5479,7 +5479,7 @@
         <v>130</v>
       </c>
       <c r="AB26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC26" t="n">
         <v>7.4</v>
@@ -5488,7 +5488,7 @@
         <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="n">
         <v>12.5</v>
@@ -5500,13 +5500,13 @@
         <v>25</v>
       </c>
       <c r="AI26" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
         <v>65</v>
@@ -5515,16 +5515,16 @@
         <v>230</v>
       </c>
       <c r="AN26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO26" t="n">
         <v>140</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR26" t="n">
         <v>8.800000000000001</v>
@@ -5533,7 +5533,7 @@
         <v>11.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
@@ -5560,7 +5560,7 @@
         <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
@@ -5569,14 +5569,14 @@
         <v>12</v>
       </c>
       <c r="BF26" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
         <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H29" t="n">
         <v>2.28</v>
@@ -6007,158 +6007,158 @@
         <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>1.62</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P29" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
         <v>1.66</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y29" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX29" t="n">
         <v>20</v>
       </c>
-      <c r="AA29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AY29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB29" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BC29" t="n">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.56</v>
+        <v>9.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.62</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G30" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="J30" t="n">
         <v>3</v>
@@ -6210,13 +6210,13 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P30" t="n">
         <v>1.73</v>
@@ -6225,58 +6225,58 @@
         <v>1.99</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6294,7 +6294,7 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>1.03</v>
@@ -6348,11 +6348,11 @@
         <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -6383,34 +6383,34 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
         <v>1.57</v>
@@ -6419,134 +6419,134 @@
         <v>2.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH31" t="n">
         <v>23</v>
       </c>
-      <c r="AE31" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>28</v>
-      </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
         <v>32</v>
       </c>
-      <c r="AK31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="AT31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BA31" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
         <v>2.34</v>
@@ -766,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -781,16 +781,16 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
         <v>1.49</v>
@@ -805,7 +805,7 @@
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
         <v>1.74</v>
@@ -814,46 +814,46 @@
         <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
         <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
         <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>85</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G7" t="n">
         <v>1.75</v>
@@ -1736,7 +1736,7 @@
         <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -1748,76 +1748,76 @@
         <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
         <v>46</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
         <v>18</v>
@@ -1829,25 +1829,25 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
         <v>8.4</v>
@@ -1859,7 +1859,7 @@
         <v>55</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
@@ -1868,7 +1868,7 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>15</v>
@@ -1877,20 +1877,20 @@
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
@@ -2515,13 +2515,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2530,13 +2530,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.26</v>
@@ -2545,7 +2545,7 @@
         <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.71</v>
@@ -2554,7 +2554,7 @@
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.4</v>
+        <v>2.74</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="AX11" t="n">
         <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5</v>
       </c>
-      <c r="BD11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
         <v>3.75</v>
@@ -2712,7 +2712,7 @@
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2730,7 +2730,7 @@
         <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.22</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H13" t="n">
         <v>5.3</v>
@@ -2906,7 +2906,7 @@
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -2915,13 +2915,13 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
         <v>2.14</v>
@@ -2930,19 +2930,19 @@
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -2960,13 +2960,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,10 +3005,10 @@
         <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3020,7 +3020,7 @@
         <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3032,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3041,20 +3041,20 @@
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,16 +3109,16 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>1.32</v>
@@ -3127,10 +3127,10 @@
         <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3205,7 +3205,7 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
         <v>2.72</v>
       </c>
       <c r="I15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.92</v>
       </c>
       <c r="K15" t="n">
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -3306,7 +3306,7 @@
         <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.71</v>
@@ -3321,25 +3321,25 @@
         <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -3348,10 +3348,10 @@
         <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
@@ -3363,7 +3363,7 @@
         <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3420,7 +3420,7 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB15" t="n">
         <v>1.03</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
         <v>5.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3500,13 +3500,13 @@
         <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
         <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
         <v>1.31</v>
@@ -3524,7 +3524,7 @@
         <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="X16" t="n">
         <v>14</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
         <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
@@ -3703,7 +3703,7 @@
         <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
         <v>2.22</v>
@@ -3712,13 +3712,13 @@
         <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
         <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
         <v>27</v>
@@ -3730,7 +3730,7 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB17" t="n">
         <v>28</v>
@@ -3745,7 +3745,7 @@
         <v>970</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG17" t="n">
         <v>23</v>
@@ -3760,7 +3760,7 @@
         <v>120</v>
       </c>
       <c r="AK17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL17" t="n">
         <v>60</v>
@@ -3772,65 +3772,65 @@
         <v>48</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB17" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG17" t="n">
         <v>5.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
         <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -3906,7 +3906,7 @@
         <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
@@ -4082,7 +4082,7 @@
         <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
         <v>1.6</v>
@@ -4097,13 +4097,13 @@
         <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
         <v>1.63</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4196,10 +4196,10 @@
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BC19" t="n">
         <v>1.03</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I20" t="n">
         <v>3.85</v>
@@ -4273,40 +4273,40 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
       </c>
       <c r="P20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.92</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
         <v>29</v>
@@ -4318,7 +4318,7 @@
         <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
         <v>17</v>
@@ -4327,7 +4327,7 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -4342,7 +4342,7 @@
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
         <v>44</v>
@@ -4351,7 +4351,7 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>46</v>
@@ -4360,10 +4360,10 @@
         <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>4.8</v>
@@ -4372,16 +4372,16 @@
         <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
         <v>8.6</v>
@@ -4396,7 +4396,7 @@
         <v>4.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
         <v>4.6</v>
@@ -4405,14 +4405,14 @@
         <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
         <v>4.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.56</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4476,7 +4476,7 @@
         <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
         <v>1.35</v>
@@ -4485,16 +4485,16 @@
         <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
         <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4661,13 +4661,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
         <v>1.89</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>1.34</v>
       </c>
       <c r="G23" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4864,25 +4864,25 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
         <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U23" t="n">
         <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -4900,10 +4900,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4912,22 +4912,22 @@
         <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4942,13 +4942,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>23</v>
+        <v>4.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -4957,10 +4957,10 @@
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4969,10 +4969,10 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
@@ -4981,20 +4981,20 @@
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF23" t="n">
         <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="G24" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="I24" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="J24" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
         <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5136,7 +5136,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR24" t="n">
         <v>1.03</v>
@@ -5148,7 +5148,7 @@
         <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
         <v>1.03</v>
@@ -5184,11 +5184,11 @@
         <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>2.28</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>2.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5419,37 +5419,37 @@
         <v>2.24</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
         <v>5.5</v>
@@ -5458,7 +5458,7 @@
         <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5497,10 +5497,10 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI26" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
@@ -5518,19 +5518,19 @@
         <v>34</v>
       </c>
       <c r="AO26" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT26" t="n">
         <v>6</v>
@@ -5542,7 +5542,7 @@
         <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5554,29 +5554,29 @@
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD26" t="n">
         <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5804,19 @@
         <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I28" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J28" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,22 +5825,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="O28" t="n">
         <v>1.01</v>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R28" t="n">
         <v>1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H29" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I29" t="n">
         <v>2.5</v>
@@ -6010,19 +6010,19 @@
         <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
         <v>1.59</v>
@@ -6034,10 +6034,10 @@
         <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.83</v>
@@ -6046,7 +6046,7 @@
         <v>1.66</v>
       </c>
       <c r="W29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X29" t="n">
         <v>10.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -6231,10 +6231,10 @@
         <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V30" t="n">
         <v>2.06</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G31" t="n">
         <v>2.2</v>
@@ -6395,7 +6395,7 @@
         <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>3.35</v>
@@ -6407,13 +6407,13 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P31" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q31" t="n">
         <v>2.46</v>
@@ -6431,7 +6431,7 @@
         <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
         <v>1.83</v>
@@ -6485,22 +6485,22 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6.4</v>
@@ -6509,10 +6509,10 @@
         <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6521,32 +6521,32 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF31" t="n">
         <v>6.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
         <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -778,10 +778,10 @@
         <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -790,7 +790,7 @@
         <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.49</v>
@@ -805,64 +805,64 @@
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
         <v>1.74</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="n">
         <v>21</v>
       </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1745,34 +1745,34 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
@@ -1784,16 +1784,16 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
         <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
         <v>9.199999999999999</v>
@@ -1802,10 +1802,10 @@
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
@@ -1820,10 +1820,10 @@
         <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1832,31 +1832,31 @@
         <v>9.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
         <v>9.4</v>
@@ -1868,29 +1868,29 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.66</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2077,14 +2077,14 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
         <v>1000</v>
@@ -2223,10 +2223,10 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
         <v>1.03</v>
@@ -2235,13 +2235,13 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
@@ -2250,10 +2250,10 @@
         <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2309,118 +2309,118 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.21</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -2429,34 +2429,34 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
@@ -2465,14 +2465,14 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2536,25 +2536,25 @@
         <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
         <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2569,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2581,10 +2581,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AS11" t="n">
-        <v>1.47</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
         <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -2733,10 +2733,10 @@
         <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2921,28 +2921,28 @@
         <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
         <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -2960,7 +2960,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
         <v>27</v>
@@ -3005,10 +3005,10 @@
         <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3020,7 +3020,7 @@
         <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3032,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3041,20 +3041,20 @@
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
         <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3115,10 +3115,10 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
         <v>1.32</v>
@@ -3127,16 +3127,16 @@
         <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,10 +3163,10 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,10 +3193,10 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
         <v>1.03</v>
@@ -3205,10 +3205,10 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
         <v>1.03</v>
@@ -3229,10 +3229,10 @@
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
         <v>1.03</v>
@@ -3244,11 +3244,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3297,7 +3297,7 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -3309,13 +3309,13 @@
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
         <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
         <v>4.1</v>
@@ -3330,13 +3330,13 @@
         <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
         <v>22</v>
@@ -3348,16 +3348,16 @@
         <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>15</v>
@@ -3399,7 +3399,7 @@
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU15" t="n">
         <v>5.8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
         <v>3.3</v>
@@ -3503,37 +3503,37 @@
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
         <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3545,10 +3545,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -3560,83 +3560,83 @@
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15</v>
       </c>
-      <c r="AO16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>17</v>
-      </c>
       <c r="BA16" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H17" t="n">
         <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3694,34 +3694,34 @@
         <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
         <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U17" t="n">
         <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W17" t="n">
         <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
@@ -3730,10 +3730,10 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AC17" t="n">
         <v>970</v>
@@ -3745,92 +3745,92 @@
         <v>970</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG17" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H18" t="n">
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3891,10 +3891,10 @@
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -3903,16 +3903,16 @@
         <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3951,11 +3951,11 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AK18" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL18" t="n">
         <v>1000</v>
       </c>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.2</v>
+        <v>1.22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>1.26</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.66</v>
+        <v>1.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.65</v>
+        <v>1.28</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.55</v>
+        <v>1.46</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.3</v>
+        <v>1.23</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.95</v>
+        <v>1.28</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>1.28</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4055,40 +4055,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
         <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
         <v>1.47</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R19" t="n">
         <v>1.21</v>
@@ -4097,19 +4097,19 @@
         <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
@@ -4127,7 +4127,7 @@
         <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -4139,13 +4139,13 @@
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
         <v>34</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR19" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
         <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BE19" t="n">
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
         <v>50</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
         <v>3.25</v>
       </c>
       <c r="I20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>3.3</v>
@@ -4291,7 +4291,7 @@
         <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
         <v>2.08</v>
@@ -4306,13 +4306,13 @@
         <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -4324,37 +4324,37 @@
         <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
       </c>
       <c r="AI20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>11</v>
@@ -4366,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4378,41 +4378,41 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF20" t="n">
         <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.56</v>
       </c>
       <c r="G21" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
         <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4473,7 +4473,7 @@
         <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
         <v>1.89</v>
@@ -4491,10 +4491,10 @@
         <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>1.84</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,34 +4661,34 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4831,28 +4831,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G23" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="H23" t="n">
         <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K23" t="n">
         <v>5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>3.9</v>
@@ -4861,7 +4861,7 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
         <v>1.84</v>
@@ -4879,10 +4879,10 @@
         <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -4903,7 +4903,7 @@
         <v>13</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4915,7 +4915,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4924,10 +4924,10 @@
         <v>11.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4939,28 +4939,28 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU23" t="n">
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4969,32 +4969,32 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE23" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G24" t="n">
         <v>6.4</v>
@@ -5034,13 +5034,13 @@
         <v>1.83</v>
       </c>
       <c r="I24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
@@ -5049,7 +5049,7 @@
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>1.39</v>
@@ -5058,7 +5058,7 @@
         <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5073,10 +5073,10 @@
         <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5181,14 +5181,14 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BG24" t="n">
         <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5222,22 +5222,22 @@
         <v>2.28</v>
       </c>
       <c r="G25" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="K25" t="n">
         <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -5258,7 +5258,7 @@
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
@@ -5267,52 +5267,52 @@
         <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
         <v>10.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA25" t="n">
         <v>95</v>
       </c>
       <c r="AB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC25" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="n">
         <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="n">
         <v>70</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G26" t="n">
         <v>2.24</v>
@@ -5422,7 +5422,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -5431,34 +5431,34 @@
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
         <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5467,19 +5467,19 @@
         <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC26" t="n">
         <v>7.4</v>
@@ -5497,10 +5497,10 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI26" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
@@ -5512,25 +5512,25 @@
         <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR26" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AS26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
         <v>6</v>
@@ -5542,7 +5542,7 @@
         <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5551,32 +5551,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD26" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>3.95</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I28" t="n">
         <v>3.55</v>
@@ -5834,13 +5834,13 @@
         <v>1.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R28" t="n">
         <v>1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
         <v>3.7</v>
@@ -6007,7 +6007,7 @@
         <v>2.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
         <v>3.5</v>
@@ -6025,22 +6025,22 @@
         <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V29" t="n">
         <v>1.66</v>
@@ -6049,73 +6049,73 @@
         <v>1.37</v>
       </c>
       <c r="X29" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AE29" t="n">
         <v>38</v>
       </c>
-      <c r="AB29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>34</v>
-      </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AK29" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
@@ -6124,7 +6124,7 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
@@ -6136,29 +6136,29 @@
         <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I30" t="n">
         <v>1.94</v>
@@ -6207,7 +6207,7 @@
         <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
@@ -6231,10 +6231,10 @@
         <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
         <v>2.06</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G31" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6410,73 +6410,73 @@
         <v>2.76</v>
       </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>80</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK31" t="n">
         <v>29</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>30</v>
       </c>
       <c r="AL31" t="n">
         <v>60</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
       </c>
       <c r="AR31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS31" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS31" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AT31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW31" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AX31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD31" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>42</v>
-      </c>
       <c r="BE31" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -778,10 +778,10 @@
         <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -808,119 +808,119 @@
         <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>17</v>
       </c>
-      <c r="AC2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AI2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG2" t="n">
         <v>21</v>
       </c>
-      <c r="AE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V6" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>5.9</v>
@@ -1745,31 +1745,31 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
         <v>2.12</v>
@@ -1778,46 +1778,46 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
       </c>
       <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
         <v>70</v>
       </c>
-      <c r="AF7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>75</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -1826,10 +1826,10 @@
         <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>75</v>
@@ -1838,28 +1838,28 @@
         <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
         <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
@@ -1868,7 +1868,7 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>15.5</v>
@@ -1877,20 +1877,20 @@
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2118,25 +2118,25 @@
         <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
         <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
         <v>3.3</v>
@@ -2148,22 +2148,22 @@
         <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>1.42</v>
@@ -2184,7 +2184,7 @@
         <v>13.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2309,118 +2309,118 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.29</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP10" t="n">
         <v>12</v>
       </c>
-      <c r="AO10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -2429,50 +2429,50 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>3.65</v>
@@ -2521,7 +2521,7 @@
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2533,10 +2533,10 @@
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.7</v>
       </c>
-      <c r="I12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
         <v>1.01</v>
@@ -2727,16 +2727,16 @@
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2924,7 +2924,7 @@
         <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -2933,13 +2933,13 @@
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>2.16</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>1.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>6.8</v>
@@ -3103,7 +3103,7 @@
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3130,7 +3130,7 @@
         <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
         <v>2.78</v>
@@ -3297,7 +3297,7 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -3336,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
         <v>22</v>
@@ -3351,10 +3351,10 @@
         <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
@@ -3372,7 +3372,7 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3393,13 +3393,13 @@
         <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
         <v>5.8</v>
@@ -3411,25 +3411,25 @@
         <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
         <v>38</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
         <v>1.92</v>
@@ -3482,28 +3482,28 @@
         <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
         <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
@@ -3515,7 +3515,7 @@
         <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
         <v>1.91</v>
@@ -3530,52 +3530,52 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>120</v>
@@ -3584,59 +3584,59 @@
         <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT16" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT16" t="n">
-        <v>6</v>
-      </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>50</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
         <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H17" t="n">
         <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3697,64 +3697,64 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S17" t="n">
         <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3766,71 +3766,71 @@
         <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
         <v>4.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
         <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G18" t="n">
         <v>1.54</v>
@@ -3873,13 +3873,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3894,16 +3894,16 @@
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>1.96</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3951,10 +3951,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.23</v>
+        <v>2.48</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.28</v>
+        <v>2.68</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.71</v>
+        <v>3.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.27</v>
+        <v>2.64</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.46</v>
+        <v>3.65</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.47</v>
+        <v>7.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.23</v>
+        <v>2.46</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.27</v>
+        <v>2.64</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.28</v>
+        <v>2.36</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.24</v>
+        <v>2.54</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4055,100 +4055,100 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
         <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
         <v>25</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4157,68 +4157,68 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU19" t="n">
         <v>5.7</v>
       </c>
       <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX19" t="n">
         <v>12</v>
       </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
         <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BG19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -4273,7 +4273,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
@@ -4282,10 +4282,10 @@
         <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
         <v>3.35</v>
@@ -4297,31 +4297,31 @@
         <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X20" t="n">
         <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4333,13 +4333,13 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
         <v>1000</v>
@@ -4354,65 +4354,65 @@
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP20" t="n">
         <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
         <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4446,22 @@
         <v>2.56</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H21" t="n">
         <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4473,10 +4473,10 @@
         <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
         <v>1.35</v>
@@ -4491,10 +4491,10 @@
         <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -4569,7 +4569,7 @@
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,25 +4703,25 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4739,16 +4739,16 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
         <v>1.03</v>
@@ -4757,34 +4757,34 @@
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
         <v>1.03</v>
@@ -4793,14 +4793,14 @@
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4840,16 +4840,16 @@
         <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K23" t="n">
         <v>5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4861,7 +4861,7 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>1.84</v>
@@ -4879,7 +4879,7 @@
         <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
         <v>3.85</v>
@@ -4888,7 +4888,7 @@
         <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
         <v>13</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -4924,7 +4924,7 @@
         <v>11.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>60</v>
@@ -4939,16 +4939,16 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
@@ -4957,10 +4957,10 @@
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4969,32 +4969,32 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
         <v>34</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
         <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5031,52 +5031,52 @@
         <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="I24" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5136,7 +5136,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
         <v>1.03</v>
@@ -5181,14 +5181,14 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5219,31 +5219,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="O25" t="n">
         <v>1.48</v>
@@ -5258,7 +5258,7 @@
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
@@ -5267,16 +5267,16 @@
         <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z25" t="n">
         <v>29</v>
@@ -5291,10 +5291,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
         <v>16.5</v>
@@ -5312,7 +5312,7 @@
         <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL25" t="n">
         <v>70</v>
@@ -5321,7 +5321,7 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO25" t="n">
         <v>90</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5413,52 +5413,52 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
         <v>2.24</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.56</v>
       </c>
       <c r="P26" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T26" t="n">
         <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5467,70 +5467,70 @@
         <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="n">
         <v>29</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>25</v>
       </c>
       <c r="AI26" t="n">
         <v>120</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>6</v>
@@ -5539,10 +5539,10 @@
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5551,32 +5551,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5801,46 +5801,46 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="H28" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I28" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R28" t="n">
         <v>1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -6010,34 +6010,34 @@
         <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.81</v>
@@ -6052,25 +6052,25 @@
         <v>12</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA29" t="n">
         <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
         <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF29" t="n">
         <v>28</v>
@@ -6079,10 +6079,10 @@
         <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ29" t="n">
         <v>90</v>
@@ -6100,10 +6100,10 @@
         <v>85</v>
       </c>
       <c r="AO29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.8</v>
@@ -6130,7 +6130,7 @@
         <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ29" t="n">
         <v>19.5</v>
@@ -6151,14 +6151,14 @@
         <v>4.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG29" t="n">
         <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
         <v>1.74</v>
       </c>
       <c r="I30" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="J30" t="n">
         <v>3</v>
@@ -6207,10 +6207,10 @@
         <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
         <v>2.84</v>
@@ -6219,28 +6219,28 @@
         <v>1.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
         <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
         <v>1.84</v>
       </c>
       <c r="V30" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
         <v>15</v>
@@ -6252,7 +6252,7 @@
         <v>12.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="n">
         <v>19.5</v>
@@ -6267,7 +6267,7 @@
         <v>26</v>
       </c>
       <c r="AF30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG30" t="n">
         <v>26</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -6389,10 +6389,10 @@
         <v>2.16</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>3.15</v>
@@ -6401,7 +6401,7 @@
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
@@ -6416,7 +6416,7 @@
         <v>1.57</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R31" t="n">
         <v>1.21</v>
@@ -6440,46 +6440,46 @@
         <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6491,16 +6491,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6509,10 +6509,10 @@
         <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
         <v>9.800000000000001</v>
@@ -6521,32 +6521,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
         <v>18</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pohronie</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Puchov</t>
+          <t>Al Jubail</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.95</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="K2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
         <v>4.4</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.69</v>
-      </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Triglav</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rudar</t>
+          <t>FK Puchov</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NK Slovenska Bistrica</t>
+          <t>Triglav</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Rudar</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NK Brinje Grosuplje</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1366,19 +1366,19 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,73 +1524,73 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,10 +1602,10 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1689,21 +1689,21 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thisted</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2106,67 +2106,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fremad Amager</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,10 +2223,10 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
         <v>1.03</v>
@@ -2235,13 +2235,13 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
@@ -2250,10 +2250,10 @@
         <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roskilde</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.75</v>
       </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.6</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG10" t="n">
         <v>21</v>
       </c>
-      <c r="Z10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>40</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.68</v>
       </c>
-      <c r="H11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.16</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
         <v>12</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2688,70 +2688,70 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2882,109 +2882,109 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY13" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY13" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>75</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S14" t="n">
         <v>4.2</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF14" t="n">
         <v>11</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>13</v>
-      </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
         <v>12.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>65</v>
+        <v>5.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.98</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
-        <v>2.78</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W15" t="n">
         <v>2.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
         <v>13</v>
       </c>
-      <c r="Y15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>34</v>
-      </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="G16" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.2</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I17" t="n">
         <v>5.8</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR17" t="n">
         <v>4.6</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>10</v>
-      </c>
       <c r="AS17" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
         <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.54</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="I18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>4.5</v>
       </c>
-      <c r="K18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.66</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76</v>
+        <v>1.54</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4.4</v>
       </c>
-      <c r="T19" t="n">
+      <c r="AV19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BD19" t="n">
         <v>1.98</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X19" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BF19" t="n">
-        <v>27</v>
+        <v>3.55</v>
       </c>
       <c r="BG19" t="n">
-        <v>44</v>
+        <v>2.04</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="G20" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.35</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
         <v>30</v>
       </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC20" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="BG20" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
         <v>14</v>
       </c>
-      <c r="Z21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="BG21" t="n">
         <v>50</v>
       </c>
-      <c r="AB21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -4628,163 +4628,163 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y22" t="n">
         <v>14</v>
       </c>
-      <c r="Y22" t="n">
-        <v>16</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>13</v>
       </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>15</v>
-      </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
         <v>1.03</v>
@@ -4793,14 +4793,14 @@
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>50</v>
+        <v>17.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.32</v>
+        <v>2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP23" t="n">
         <v>11</v>
       </c>
-      <c r="I23" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="AQ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.3</v>
       </c>
-      <c r="K23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="X23" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BF23" t="n">
         <v>13.5</v>
       </c>
-      <c r="BD23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="G24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW24" t="n">
         <v>6.4</v>
       </c>
-      <c r="H24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="AX24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF24" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>80</v>
-      </c>
       <c r="BG24" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.72</v>
+        <v>6.4</v>
       </c>
       <c r="H25" t="n">
-        <v>3.15</v>
+        <v>1.86</v>
       </c>
       <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
         <v>4.1</v>
       </c>
-      <c r="J25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG25" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>5.6</v>
+        <v>1.02</v>
       </c>
       <c r="T26" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.48</v>
+        <v>2.72</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.48</v>
+        <v>5.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,55 +5792,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="R28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="G29" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H29" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>32</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,108 +6175,108 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Palmeiras (W)</t>
+          <t>Richmond Kickers</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.3</v>
+        <v>1.61</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="H30" t="n">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>1.68</v>
       </c>
       <c r="O30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>1.86</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.94</v>
+        <v>1.14</v>
       </c>
       <c r="W30" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
@@ -6294,7 +6294,7 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
         <v>1.03</v>
@@ -6348,18 +6348,18 @@
         <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,960 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R31" t="n">
         <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="W31" t="n">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="X31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD31" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT31" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
         <v>6.6</v>
       </c>
       <c r="AV31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>La Luz FC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazilian Campeonato Women</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sao Paulo (W)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Palmeiras (W)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>22:10:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H35" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD35" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF31" t="n">
+      <c r="BE35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF35" t="n">
         <v>18</v>
       </c>
-      <c r="BG31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-03-26 09:35:26</t>
+      <c r="BG35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
         <v>1.3</v>
@@ -772,13 +772,13 @@
         <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
         <v>1.1</v>
@@ -790,13 +790,13 @@
         <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Serbian First League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pohronie</t>
+          <t>FK Usce Novi Beograd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Puchov</t>
+          <t>Tekstilac Odzaci</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.05</v>
       </c>
-      <c r="N3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.66</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,179 +1136,179 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Triglav</t>
+          <t>Pohronie</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rudar</t>
+          <t>FK Puchov</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21</v>
+        <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NK Slovenska Bistrica</t>
+          <t>Triglav</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Rudar</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NK Brinje Grosuplje</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,73 +1718,73 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1883,21 +1883,21 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Union Comercio</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thisted</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.23</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -2300,127 +2300,127 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fremad Amager</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -2429,34 +2429,34 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
@@ -2465,14 +2465,14 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Roskilde</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
         <v>21</v>
       </c>
-      <c r="Z11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BG11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>40</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,75 +2683,75 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.49</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.61</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,99 +2775,99 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AG12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AW12" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,132 +2877,132 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>1.93</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>2.28</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P13" t="n">
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
         <v>1.03</v>
@@ -3011,34 +3011,34 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
         <v>1.03</v>
@@ -3047,14 +3047,14 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>75</v>
+        <v>13.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
         <v>12</v>
       </c>
-      <c r="Y14" t="n">
-        <v>18</v>
-      </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
         <v>27</v>
       </c>
-      <c r="AE14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BG14" t="n">
         <v>28</v>
       </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -3270,70 +3270,70 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.72</v>
       </c>
-      <c r="H15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>65</v>
+        <v>5.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
         <v>4.1</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AS16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
         <v>15</v>
       </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>28</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>22</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
         <v>6</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.2</v>
+        <v>65</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,105 +4041,105 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.47</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4157,75 +4157,75 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.94</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.02</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.58</v>
+        <v>5.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.92</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.55</v>
+        <v>26</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,105 +4235,105 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="K20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.35</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4357,43 +4357,43 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
         <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
         <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
         <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
         <v>1.03</v>
@@ -4405,21 +4405,21 @@
         <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,78 +4429,78 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,25 +4509,25 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
@@ -4545,16 +4545,16 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
         <v>1.03</v>
@@ -4563,34 +4563,34 @@
         <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
         <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
         <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
         <v>1.03</v>
@@ -4599,14 +4599,14 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -4628,37 +4628,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
         <v>3.7</v>
@@ -4667,140 +4667,140 @@
         <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.73</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.51</v>
-      </c>
       <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR22" t="n">
         <v>19</v>
       </c>
-      <c r="Y22" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="AS22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>30</v>
       </c>
-      <c r="AP22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>21</v>
-      </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF22" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -4822,100 +4822,100 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="G23" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
         <v>16</v>
       </c>
       <c r="Z23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
         <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.32</v>
+        <v>2.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.35</v>
+        <v>2.96</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>2.92</v>
       </c>
       <c r="J24" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>5.9</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="W24" t="n">
-        <v>3.85</v>
+        <v>1.51</v>
       </c>
       <c r="X24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW24" t="n">
         <v>21</v>
       </c>
-      <c r="Y24" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AX24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>13</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW25" t="n">
         <v>6.4</v>
       </c>
-      <c r="H25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ25" t="n">
+      <c r="AX25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF25" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>80</v>
-      </c>
       <c r="BG25" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
         <v>2.8</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.28</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X26" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF26" t="n">
         <v>27</v>
       </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="BG26" t="n">
         <v>44</v>
       </c>
-      <c r="AK26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="G27" t="n">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.25</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="X27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
         <v>10</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AD27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="n">
         <v>22</v>
       </c>
-      <c r="AE27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>38</v>
-      </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW27" t="n">
         <v>5.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
         <v>5.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,72 +5787,72 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="n">
         <v>1.25</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.48</v>
-      </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5909,69 +5909,69 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="G29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.55</v>
       </c>
-      <c r="H29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG29" t="n">
         <v>3.25</v>
       </c>
-      <c r="J29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>32</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,73 +6175,73 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>One Knoxville SC</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Richmond Kickers</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.61</v>
+        <v>4.5</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="R30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.18</v>
       </c>
-      <c r="S30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.9</v>
-      </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
@@ -6297,69 +6297,69 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="G31" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="H31" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.81</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AA31" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.6</v>
+        <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,114 +6563,114 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spokane Velocity FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="H32" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="P32" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.78</v>
+        <v>5.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
@@ -6679,13 +6679,13 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.03</v>
@@ -6700,7 +6700,7 @@
         <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV32" t="n">
         <v>1.03</v>
@@ -6709,7 +6709,7 @@
         <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
         <v>1.03</v>
@@ -6733,21 +6733,21 @@
         <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,60 +6757,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O33" t="n">
         <v>1.02</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.01</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,108 +6951,108 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sao Paulo (W)</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Palmeiras (W)</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>4.3</v>
       </c>
-      <c r="G34" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U34" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V34" t="n">
-        <v>2.08</v>
+        <v>1.46</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="X34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
         <v>1000</v>
@@ -7070,7 +7070,7 @@
         <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
         <v>1.03</v>
@@ -7124,18 +7124,18 @@
         <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 11:44:06</t>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,184 +7145,1154 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22:10:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Richmond Kickers</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="n">
         <v>4.2</v>
       </c>
       <c r="I35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S36" t="n">
         <v>5</v>
       </c>
-      <c r="J35" t="n">
+      <c r="T36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brazilian Campeonato Women</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sao Paulo (W)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Palmeiras (W)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X38" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>La Luz FC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22:10:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
         <v>3.1</v>
       </c>
-      <c r="K35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="K40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L40" t="n">
         <v>1.47</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M40" t="n">
         <v>1.11</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N40" t="n">
         <v>2.72</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O40" t="n">
         <v>1.5</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P40" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q40" t="n">
         <v>2.46</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R40" t="n">
         <v>1.21</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR40" t="n">
         <v>4.7</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X35" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS35" t="n">
+      <c r="AS40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW40" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW35" t="n">
+      <c r="AX40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD40" t="n">
         <v>5</v>
       </c>
-      <c r="AX35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE35" t="n">
+      <c r="BE40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG40" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF35" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>2026-03-26 11:44:06</t>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:55:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -760,19 +760,19 @@
         <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -784,7 +784,7 @@
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
         <v>2.44</v>
@@ -808,7 +808,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,13 +981,13 @@
         <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
         <v>1.05</v>
@@ -999,10 +999,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
@@ -1172,13 +1172,13 @@
         <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
         <v>1.5</v>
@@ -1193,7 +1193,7 @@
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.79</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
@@ -1372,19 +1372,19 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
         <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1560,10 +1560,10 @@
         <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
@@ -1572,25 +1572,25 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
         <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
@@ -1602,7 +1602,7 @@
         <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1638,19 +1638,19 @@
         <v>7.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1662,19 +1662,19 @@
         <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
         <v>15</v>
@@ -1686,17 +1686,17 @@
         <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1933,34 +1933,34 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.02</v>
       </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R8" t="n">
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.36</v>
@@ -2721,19 +2721,19 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
         <v>3.6</v>
@@ -2742,7 +2742,7 @@
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
         <v>1.49</v>
@@ -2817,7 +2817,7 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
         <v>5.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="I13" t="n">
         <v>2.28</v>
@@ -2915,7 +2915,7 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.35</v>
@@ -2924,13 +2924,13 @@
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.82</v>
@@ -2942,7 +2942,7 @@
         <v>1.79</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,25 +2999,25 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
@@ -3026,7 +3026,7 @@
         <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.03</v>
@@ -3047,14 +3047,14 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BG13" t="n">
         <v>13.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H14" t="n">
         <v>2.78</v>
@@ -3100,10 +3100,10 @@
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3112,10 +3112,10 @@
         <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
         <v>2.2</v>
@@ -3136,7 +3136,7 @@
         <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -3151,22 +3151,22 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -3199,7 +3199,7 @@
         <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
         <v>1.03</v>
@@ -3223,7 +3223,7 @@
         <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
@@ -3232,7 +3232,7 @@
         <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BD14" t="n">
         <v>1.03</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I15" t="n">
         <v>9.800000000000001</v>
@@ -3297,7 +3297,7 @@
         <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -3318,7 +3318,7 @@
         <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
         <v>2.18</v>
@@ -3330,7 +3330,7 @@
         <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC15" t="n">
         <v>10.5</v>
@@ -3387,28 +3387,28 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>5.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -3417,32 +3417,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
@@ -3500,16 +3500,16 @@
         <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
         <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
         <v>3.8</v>
@@ -3518,7 +3518,7 @@
         <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -3673,19 +3673,19 @@
         <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3697,7 +3697,7 @@
         <v>1.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q17" t="n">
         <v>2.32</v>
@@ -3712,7 +3712,7 @@
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -3742,7 +3742,7 @@
         <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
         <v>11</v>
@@ -3763,74 +3763,74 @@
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AX17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -3861,46 +3861,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
         <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
         <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
         <v>1.9</v>
@@ -3909,10 +3909,10 @@
         <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,7 +3972,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
         <v>1.03</v>
@@ -3981,7 +3981,7 @@
         <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -3996,7 +3996,7 @@
         <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.03</v>
@@ -4005,10 +4005,10 @@
         <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
         <v>1.03</v>
@@ -4017,14 +4017,14 @@
         <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
         <v>3.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,19 +4079,19 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>4.3</v>
@@ -4100,7 +4100,7 @@
         <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4109,7 +4109,7 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4175,13 +4175,13 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
@@ -4190,7 +4190,7 @@
         <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
@@ -4211,14 +4211,14 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="G20" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J20" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,22 +4273,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
         <v>3.8</v>
@@ -4455,10 +4455,10 @@
         <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -4694,10 +4694,10 @@
         <v>17</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>17.5</v>
@@ -4718,7 +4718,7 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
@@ -4730,7 +4730,7 @@
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4748,37 +4748,37 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="AS22" t="n">
         <v>5.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>36</v>
+        <v>5.1</v>
       </c>
       <c r="BB22" t="n">
         <v>6.4</v>
@@ -4787,7 +4787,7 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
         <v>5.3</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5034,16 +5034,16 @@
         <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -5058,7 +5058,7 @@
         <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -5076,7 +5076,7 @@
         <v>1.52</v>
       </c>
       <c r="W24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
         <v>19</v>
@@ -5136,7 +5136,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
         <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
         <v>1.07</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
         <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.79</v>
       </c>
       <c r="G27" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H27" t="n">
         <v>5.3</v>
@@ -5649,7 +5649,7 @@
         <v>3.65</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
         <v>1.92</v>
@@ -5667,34 +5667,34 @@
         <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA27" t="n">
         <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
         <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -5709,7 +5709,7 @@
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>110</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5736,7 +5736,7 @@
         <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="AX27" t="n">
         <v>8</v>
@@ -5748,7 +5748,7 @@
         <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>55</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5757,20 +5757,20 @@
         <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF27" t="n">
         <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="G29" t="n">
         <v>5.5</v>
@@ -6004,10 +6004,10 @@
         <v>1.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>4.6</v>
@@ -6025,10 +6025,10 @@
         <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R29" t="n">
         <v>1.61</v>
@@ -6037,13 +6037,13 @@
         <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U29" t="n">
         <v>2.36</v>
       </c>
       <c r="V29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W29" t="n">
         <v>1.22</v>
@@ -6103,7 +6103,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ29" t="n">
         <v>4.2</v>
@@ -6127,7 +6127,7 @@
         <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY29" t="n">
         <v>4.6</v>
@@ -6139,10 +6139,10 @@
         <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
         <v>5.2</v>
@@ -6151,14 +6151,14 @@
         <v>5.3</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
         <v>3.25</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.18</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
@@ -6395,13 +6395,13 @@
         <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>3.25</v>
       </c>
       <c r="L31" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
         <v>1.14</v>
@@ -6413,7 +6413,7 @@
         <v>1.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q31" t="n">
         <v>2.88</v>
@@ -6425,10 +6425,10 @@
         <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
         <v>1.28</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H32" t="n">
         <v>3.4</v>
@@ -6589,7 +6589,7 @@
         <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K32" t="n">
         <v>3.3</v>
@@ -6601,7 +6601,7 @@
         <v>1.13</v>
       </c>
       <c r="N32" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O32" t="n">
         <v>1.54</v>
@@ -6622,7 +6622,7 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V32" t="n">
         <v>1.31</v>
@@ -6631,7 +6631,7 @@
         <v>1.61</v>
       </c>
       <c r="X32" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y32" t="n">
         <v>10.5</v>
@@ -6673,19 +6673,19 @@
         <v>42</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.03</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="G34" t="n">
         <v>3.45</v>
@@ -6977,7 +6977,7 @@
         <v>3.25</v>
       </c>
       <c r="J34" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -7013,10 +7013,10 @@
         <v>1.87</v>
       </c>
       <c r="V34" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>1.58</v>
       </c>
       <c r="G35" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I35" t="n">
         <v>7.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O35" t="n">
         <v>1.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" t="n">
         <v>1.86</v>
@@ -7210,7 +7210,7 @@
         <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
         <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
         <v>2.04</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 13:55:01</t>
+          <t>2026-03-26 16:06:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I3" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>34</v>
@@ -999,10 +999,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
@@ -1172,13 +1172,13 @@
         <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
         <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
         <v>1.5</v>
@@ -1193,10 +1193,10 @@
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X4" t="n">
         <v>25</v>
@@ -1241,7 +1241,7 @@
         <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1256,59 +1256,59 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.28</v>
@@ -1557,16 +1557,16 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
         <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.56</v>
@@ -1575,7 +1575,7 @@
         <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
         <v>2.32</v>
@@ -1587,7 +1587,7 @@
         <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
         <v>24</v>
@@ -1599,7 +1599,7 @@
         <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1641,16 +1641,16 @@
         <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1659,7 +1659,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>50</v>
@@ -1668,7 +1668,7 @@
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
         <v>14</v>
@@ -1680,13 +1680,13 @@
         <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
         <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
         <v>7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2423,10 +2423,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -2438,7 +2438,7 @@
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2503,55 +2503,55 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.57</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BF11" t="n">
-        <v>21</v>
+        <v>2.34</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2811,10 +2811,10 @@
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -2826,10 +2826,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
@@ -2838,29 +2838,29 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>22</v>
+        <v>3.95</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2894,124 +2894,124 @@
         <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
         <v>5.9</v>
@@ -3020,41 +3020,41 @@
         <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BG13" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3112,7 +3112,7 @@
         <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
         <v>1.72</v>
@@ -3142,7 +3142,7 @@
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
@@ -3199,10 +3199,10 @@
         <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -3214,41 +3214,41 @@
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>13.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
         <v>27</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
         <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V15" t="n">
         <v>1.11</v>
@@ -3387,10 +3387,10 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
         <v>5.7</v>
@@ -3426,7 +3426,7 @@
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD15" t="n">
         <v>5.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
         <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3587,13 +3587,13 @@
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -3623,20 +3623,20 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H17" t="n">
         <v>5.1</v>
@@ -3706,13 +3706,13 @@
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="H18" t="n">
         <v>5.3</v>
@@ -3885,28 +3885,28 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
         <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
@@ -3942,28 +3942,28 @@
         <v>11.5</v>
       </c>
       <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
         <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>12.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3975,10 +3975,10 @@
         <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -3987,10 +3987,10 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
@@ -3999,10 +3999,10 @@
         <v>7.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4011,20 +4011,20 @@
         <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>85</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -4085,10 +4085,10 @@
         <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
@@ -4172,53 +4172,53 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
         <v>3.5</v>
@@ -4279,13 +4279,13 @@
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
         <v>3.55</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,28 +4467,28 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
         <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -4554,59 +4554,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
         <v>2.36</v>
@@ -4646,16 +4646,16 @@
         <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4676,10 +4676,10 @@
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
         <v>2.08</v>
@@ -4706,10 +4706,10 @@
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4721,7 +4721,7 @@
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4742,19 +4742,19 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT22" t="n">
         <v>8.6</v>
@@ -4763,10 +4763,10 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
@@ -4775,10 +4775,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB22" t="n">
         <v>6.4</v>
@@ -4787,20 +4787,20 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4843,10 +4843,10 @@
         <v>4.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>1.44</v>
@@ -4855,10 +4855,10 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
         <v>1.79</v>
@@ -4876,7 +4876,7 @@
         <v>1.86</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
         <v>1.27</v>
@@ -4885,10 +4885,10 @@
         <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>9</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU23" t="n">
         <v>6.2</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G24" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="H24" t="n">
         <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
@@ -5055,7 +5055,7 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
         <v>1.89</v>
@@ -5064,34 +5064,34 @@
         <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U24" t="n">
         <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
@@ -5100,13 +5100,13 @@
         <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
         <v>22</v>
@@ -5118,10 +5118,10 @@
         <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5136,22 +5136,22 @@
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -5160,7 +5160,7 @@
         <v>13.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>13</v>
@@ -5169,26 +5169,26 @@
         <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
         <v>17.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G25" t="n">
         <v>1.35</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
         <v>5.3</v>
       </c>
       <c r="K25" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.3</v>
@@ -5243,25 +5243,25 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
         <v>1.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
         <v>1.67</v>
@@ -5315,7 +5315,7 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5327,13 +5327,13 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
         <v>6.6</v>
@@ -5345,10 +5345,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX25" t="n">
         <v>6.4</v>
@@ -5357,10 +5357,10 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB25" t="n">
         <v>9</v>
@@ -5369,20 +5369,20 @@
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>5.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G26" t="n">
         <v>2.68</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
         <v>3.55</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.46</v>
@@ -5437,13 +5437,13 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q26" t="n">
         <v>2.4</v>
@@ -5482,7 +5482,7 @@
         <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
         <v>15.5</v>
@@ -5530,7 +5530,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -5542,7 +5542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5554,29 +5554,29 @@
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>27</v>
+        <v>5.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>44</v>
+        <v>5.9</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G27" t="n">
         <v>1.88</v>
@@ -5616,10 +5616,10 @@
         <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.95</v>
@@ -5631,13 +5631,13 @@
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>2.06</v>
@@ -5646,7 +5646,7 @@
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
         <v>1.9</v>
@@ -5655,34 +5655,34 @@
         <v>1.92</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X27" t="n">
         <v>15.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
         <v>48</v>
       </c>
       <c r="AA27" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
         <v>11.5</v>
@@ -5691,25 +5691,25 @@
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>110</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5760,17 +5760,17 @@
         <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
         <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
         <v>1.54</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
         <v>5.8</v>
@@ -5834,19 +5834,19 @@
         <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
         <v>1.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>1.14</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AR28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV28" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AW28" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="AY28" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC28" t="n">
         <v>1.92</v>
       </c>
-      <c r="BA28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC28" t="n">
+      <c r="BD28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE28" t="n">
         <v>1.86</v>
       </c>
-      <c r="BD28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BF28" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>4.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H29" t="n">
         <v>1.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K29" t="n">
         <v>4.6</v>
@@ -6019,10 +6019,10 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P29" t="n">
         <v>2.48</v>
@@ -6046,7 +6046,7 @@
         <v>2.16</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA29" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6213,19 +6213,19 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
         <v>3.8</v>
@@ -6234,13 +6234,13 @@
         <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
         <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6300,7 +6300,7 @@
         <v>3.35</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="AR30" t="n">
         <v>3.45</v>
@@ -6312,7 +6312,7 @@
         <v>3.7</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AV30" t="n">
         <v>3.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
         <v>2.3</v>
@@ -6407,16 +6407,16 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
@@ -6425,10 +6425,10 @@
         <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
         <v>1.28</v>
@@ -6473,7 +6473,7 @@
         <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
         <v>38</v>
@@ -6497,10 +6497,10 @@
         <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT31" t="n">
         <v>5.8</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX31" t="n">
         <v>10.5</v>
@@ -6524,7 +6524,7 @@
         <v>4.9</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB31" t="n">
         <v>5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6580,34 +6580,34 @@
         <v>2.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I32" t="n">
         <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
         <v>3.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M32" t="n">
         <v>1.13</v>
       </c>
       <c r="N32" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P32" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q32" t="n">
         <v>2.6</v>
@@ -6628,7 +6628,7 @@
         <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X32" t="n">
         <v>8.800000000000001</v>
@@ -6658,7 +6658,7 @@
         <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="n">
         <v>28</v>
@@ -6667,10 +6667,10 @@
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL32" t="n">
         <v>75</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
         <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="G34" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H34" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -7016,7 +7016,7 @@
         <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K36" t="n">
         <v>3.45</v>
@@ -7392,7 +7392,7 @@
         <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
         <v>2.04</v>
@@ -7485,10 +7485,10 @@
         <v>4.3</v>
       </c>
       <c r="AX36" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="AY36" t="n">
-        <v>13.5</v>
+        <v>3.85</v>
       </c>
       <c r="AZ36" t="n">
         <v>19.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7849,62 +7849,62 @@
         <v>15.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
         <v>1.25</v>
@@ -772,7 +772,7 @@
         <v>6.8</v>
       </c>
       <c r="K2" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -787,16 +787,16 @@
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
         <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -1151,16 +1151,16 @@
         <v>2.24</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
         <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1199,13 +1199,13 @@
         <v>1.8</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>80</v>
@@ -1217,10 +1217,10 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
         <v>18.5</v>
@@ -1229,7 +1229,7 @@
         <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
@@ -1238,10 +1238,10 @@
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1250,7 +1250,7 @@
         <v>14.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1259,56 +1259,56 @@
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
         <v>10</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1369,13 +1369,13 @@
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
         <v>1.05</v>
@@ -1387,10 +1387,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
         <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1557,13 +1557,13 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
         <v>1.69</v>
@@ -1572,34 +1572,34 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1611,19 +1611,19 @@
         <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH6" t="n">
         <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
@@ -1632,13 +1632,13 @@
         <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
         <v>7.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AP6" t="n">
         <v>18</v>
@@ -1647,56 +1647,56 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
         <v>50</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>14</v>
       </c>
-      <c r="BA6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD6" t="n">
-        <v>24</v>
-      </c>
       <c r="BE6" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BF6" t="n">
         <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
         <v>1.2</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1847,7 +1847,7 @@
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
         <v>1.03</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="I8" t="n">
         <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1972,7 +1972,7 @@
         <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2032,59 +2032,59 @@
         <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.23</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
         <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.5</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2342,7 +2342,7 @@
         <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
@@ -2360,7 +2360,7 @@
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X10" t="n">
         <v>20</v>
@@ -2399,7 +2399,7 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
         <v>21</v>
@@ -2423,10 +2423,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -2438,7 +2438,7 @@
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -2506,37 +2506,37 @@
         <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
         <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
@@ -2545,19 +2545,19 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2587,13 +2587,13 @@
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW11" t="n">
         <v>4.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.76</v>
+        <v>5.6</v>
       </c>
       <c r="BA11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.34</v>
+        <v>5.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
         <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -2712,7 +2712,7 @@
         <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.36</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2912,37 +2912,37 @@
         <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2960,7 +2960,7 @@
         <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3023,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
@@ -3032,7 +3032,7 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB13" t="n">
         <v>4.1</v>
@@ -3041,20 +3041,20 @@
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF13" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF13" t="n">
-        <v>4</v>
-      </c>
       <c r="BG13" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
         <v>2.96</v>
       </c>
       <c r="H14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
@@ -3133,7 +3133,7 @@
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3196,34 +3196,34 @@
         <v>8.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA14" t="n">
         <v>6.2</v>
@@ -3238,17 +3238,17 @@
         <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -3336,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC15" t="n">
         <v>10.5</v>
@@ -3357,10 +3357,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -3369,10 +3369,10 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3381,34 +3381,34 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -3417,22 +3417,22 @@
         <v>7.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -3632,11 +3632,11 @@
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3712,13 +3712,13 @@
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -3736,7 +3736,7 @@
         <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>27</v>
@@ -3778,16 +3778,16 @@
         <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT17" t="n">
         <v>5.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.2</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -3796,7 +3796,7 @@
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3817,20 +3817,20 @@
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
         <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -3885,7 +3885,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.31</v>
@@ -3894,28 +3894,28 @@
         <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
         <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y18" t="n">
         <v>1000</v>
@@ -3927,7 +3927,7 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
@@ -3951,10 +3951,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3975,10 +3975,10 @@
         <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -3987,22 +3987,22 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4011,20 +4011,20 @@
         <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I19" t="n">
         <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -4097,7 +4097,7 @@
         <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
         <v>1.71</v>
@@ -4130,7 +4130,7 @@
         <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF19" t="n">
         <v>23</v>
@@ -4145,10 +4145,10 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4172,53 +4172,53 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.19</v>
+        <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -4282,7 +4282,7 @@
         <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1.22</v>
@@ -4297,7 +4297,7 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="I21" t="n">
         <v>6.2</v>
@@ -4458,7 +4458,7 @@
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4473,7 +4473,7 @@
         <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q21" t="n">
         <v>2.04</v>
@@ -4488,7 +4488,7 @@
         <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -4512,7 +4512,7 @@
         <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4554,59 +4554,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.09</v>
+        <v>1.75</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.09</v>
+        <v>1.78</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
         <v>3.65</v>
@@ -4652,10 +4652,10 @@
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4667,7 +4667,7 @@
         <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
         <v>1.93</v>
@@ -4688,7 +4688,7 @@
         <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
         <v>17</v>
@@ -4721,7 +4721,7 @@
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4748,13 +4748,13 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>8.6</v>
@@ -4763,7 +4763,7 @@
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
         <v>30</v>
@@ -4775,13 +4775,13 @@
         <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
         <v>18.5</v>
@@ -4790,7 +4790,7 @@
         <v>5.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I23" t="n">
         <v>4.7</v>
@@ -4855,7 +4855,7 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.37</v>
@@ -4867,7 +4867,7 @@
         <v>2.06</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
         <v>3.8</v>
@@ -4885,7 +4885,7 @@
         <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y23" t="n">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>20</v>
@@ -4915,7 +4915,7 @@
         <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4945,10 +4945,10 @@
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.6</v>
@@ -4960,7 +4960,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4972,7 +4972,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>19.5</v>
@@ -4981,20 +4981,20 @@
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
@@ -5049,7 +5049,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.31</v>
@@ -5067,13 +5067,13 @@
         <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
         <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W24" t="n">
         <v>1.53</v>
@@ -5091,13 +5091,13 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
         <v>32</v>
@@ -5166,19 +5166,19 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD24" t="n">
         <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H25" t="n">
         <v>11.5</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
         <v>5.7</v>
@@ -5249,13 +5249,13 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
         <v>1.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
@@ -5264,13 +5264,13 @@
         <v>2.26</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X25" t="n">
         <v>21</v>
@@ -5321,7 +5321,7 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5330,13 +5330,13 @@
         <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT25" t="n">
         <v>6.2</v>
@@ -5345,10 +5345,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX25" t="n">
         <v>6.4</v>
@@ -5357,10 +5357,10 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
         <v>9</v>
@@ -5369,20 +5369,20 @@
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF25" t="n">
         <v>5.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
         <v>3.55</v>
@@ -5464,22 +5464,22 @@
         <v>1.39</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="X26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y26" t="n">
         <v>11</v>
       </c>
-      <c r="Y26" t="n">
-        <v>12</v>
-      </c>
       <c r="Z26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
@@ -5488,34 +5488,34 @@
         <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5530,7 +5530,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -5542,7 +5542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5554,29 +5554,29 @@
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>5.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
         <v>3.95</v>
@@ -5637,7 +5637,7 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
         <v>2.06</v>
@@ -5676,25 +5676,25 @@
         <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
         <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -5712,7 +5712,7 @@
         <v>15</v>
       </c>
       <c r="AO27" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
         <v>9.6</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5760,17 +5760,17 @@
         <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BF27" t="n">
         <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>1.47</v>
       </c>
       <c r="G28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I28" t="n">
         <v>8.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
         <v>5.8</v>
@@ -5834,7 +5834,7 @@
         <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
@@ -5843,7 +5843,7 @@
         <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5852,7 +5852,7 @@
         <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5870,7 +5870,7 @@
         <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD28" t="n">
         <v>1000</v>
@@ -5879,10 +5879,10 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5903,68 +5903,68 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.98</v>
+        <v>9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.77</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.87</v>
+        <v>4.2</v>
       </c>
       <c r="AT28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW28" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AX28" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AY28" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="BF28" t="n">
         <v>5.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>4.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H29" t="n">
         <v>1.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6019,13 +6019,13 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.18</v>
       </c>
       <c r="P29" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
         <v>1.54</v>
@@ -6043,10 +6043,10 @@
         <v>2.36</v>
       </c>
       <c r="V29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC29" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BD29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF29" t="n">
         <v>5.6</v>
       </c>
-      <c r="BD29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H30" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.4</v>
@@ -6213,13 +6213,13 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
         <v>2.22</v>
@@ -6234,7 +6234,7 @@
         <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
         <v>2</v>
@@ -6246,7 +6246,7 @@
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6258,7 +6258,7 @@
         <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AR30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC30" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BD30" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BE30" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H32" t="n">
         <v>3.45</v>
@@ -6589,40 +6589,40 @@
         <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.51</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2.5</v>
       </c>
-      <c r="O32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.6</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V32" t="n">
         <v>1.31</v>
@@ -6631,10 +6631,10 @@
         <v>1.62</v>
       </c>
       <c r="X32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
         <v>27</v>
@@ -6643,7 +6643,7 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6652,7 +6652,7 @@
         <v>19</v>
       </c>
       <c r="AE32" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF32" t="n">
         <v>15</v>
@@ -6661,10 +6661,10 @@
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ32" t="n">
         <v>42</v>
@@ -6673,74 +6673,74 @@
         <v>40</v>
       </c>
       <c r="AL32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP32" t="n">
         <v>7</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,22 +6795,22 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -7019,10 +7019,10 @@
         <v>1.43</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
@@ -7034,7 +7034,7 @@
         <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
         <v>1.71</v>
       </c>
       <c r="O35" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
         <v>1.71</v>
@@ -7207,7 +7207,7 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W35" t="n">
         <v>1.96</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>3.35</v>
       </c>
       <c r="G36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H36" t="n">
         <v>2.38</v>
@@ -7404,7 +7404,7 @@
         <v>1.66</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
         <v>12</v>
@@ -7419,7 +7419,7 @@
         <v>44</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>7.6</v>
@@ -7431,7 +7431,7 @@
         <v>40</v>
       </c>
       <c r="AF36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG36" t="n">
         <v>18.5</v>
@@ -7470,10 +7470,10 @@
         <v>12.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AU36" t="n">
         <v>6.6</v>
@@ -7482,41 +7482,41 @@
         <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AZ36" t="n">
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H37" t="n">
         <v>2.48</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,22 +7571,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P37" t="n">
         <v>1.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7595,10 +7595,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -7741,94 +7741,94 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="I38" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="O38" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="P38" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="U38" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="V38" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="n">
         <v>22</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>20</v>
       </c>
       <c r="AC38" t="n">
         <v>10.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE38" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF38" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AG38" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AH38" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AI38" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7846,25 +7846,25 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AR38" t="n">
         <v>3.35</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AT38" t="n">
         <v>3.75</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AV38" t="n">
         <v>3.4</v>
@@ -7873,38 +7873,38 @@
         <v>3.9</v>
       </c>
       <c r="AX38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB38" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA38" t="n">
+      <c r="BC38" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>
@@ -8132,10 +8132,10 @@
         <v>2.02</v>
       </c>
       <c r="G40" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I40" t="n">
         <v>5</v>
@@ -8144,7 +8144,7 @@
         <v>3.1</v>
       </c>
       <c r="K40" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L40" t="n">
         <v>1.47</v>
@@ -8180,7 +8180,7 @@
         <v>1.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 18:18:13</t>
+          <t>2026-03-26 20:30:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -847,10 +847,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.09</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.09</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.09</v>
+        <v>2.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
@@ -987,7 +987,7 @@
         <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S3" t="n">
         <v>1.05</v>
@@ -999,7 +999,7 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
         <v>1.09</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,7 +1286,7 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1557,34 +1557,34 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
         <v>19</v>
@@ -1593,25 +1593,25 @@
         <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AA6" t="n">
         <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>9.6</v>
@@ -1632,7 +1632,7 @@
         <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
         <v>7.8</v>
@@ -1644,19 +1644,19 @@
         <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
         <v>19.5</v>
@@ -1671,10 +1671,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
         <v>15.5</v>
@@ -1683,20 +1683,20 @@
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
         <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
         <v>50</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.2</v>
@@ -1778,7 +1778,7 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1886,11 +1886,11 @@
         <v>1.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="J8" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BF8" t="n">
         <v>1.55</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
         <v>3.8</v>
@@ -2166,7 +2166,7 @@
         <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AT9" t="n">
         <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BF9" t="n">
         <v>1.32</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2342,7 +2342,7 @@
         <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
@@ -2357,10 +2357,10 @@
         <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
         <v>20</v>
@@ -2372,7 +2372,7 @@
         <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2384,10 +2384,10 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2399,19 +2399,19 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
@@ -2423,10 +2423,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -2438,7 +2438,7 @@
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -2620,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
         <v>5.8</v>
@@ -2632,7 +2632,7 @@
         <v>5.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
         <v>5.7</v>
@@ -2644,19 +2644,19 @@
         <v>5.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BF11" t="n">
         <v>5.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -2826,10 +2826,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
@@ -2838,29 +2838,29 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
         <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -2954,10 +2954,10 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
@@ -2972,10 +2972,10 @@
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2996,7 +2996,7 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -3008,7 +3008,7 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3020,10 +3020,10 @@
         <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
@@ -3032,29 +3032,29 @@
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3148,7 +3148,7 @@
         <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
         <v>11</v>
@@ -3157,7 +3157,7 @@
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>44</v>
@@ -3172,13 +3172,13 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
         <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3187,19 +3187,19 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
         <v>6.4</v>
@@ -3208,47 +3208,47 @@
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
         <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
         <v>27</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF14" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3279,64 +3279,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
         <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
         <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
         <v>20</v>
@@ -3372,7 +3372,7 @@
         <v>180</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3387,31 +3387,31 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY15" t="n">
         <v>7.8</v>
@@ -3420,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3429,20 +3429,20 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
         <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
         <v>6.6</v>
@@ -3488,7 +3488,7 @@
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3545,10 +3545,10 @@
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
@@ -3560,7 +3560,7 @@
         <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ16" t="n">
         <v>25</v>
@@ -3572,13 +3572,13 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
         <v>9.199999999999999</v>
@@ -3587,10 +3587,10 @@
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -3614,7 +3614,7 @@
         <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
@@ -3623,20 +3623,20 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G17" t="n">
         <v>1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
         <v>6.6</v>
@@ -3712,22 +3712,22 @@
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
         <v>2.24</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3739,13 +3739,13 @@
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3757,19 +3757,19 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3781,10 +3781,10 @@
         <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>5.7</v>
@@ -3796,7 +3796,7 @@
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3817,20 +3817,20 @@
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
         <v>5.3</v>
@@ -3876,7 +3876,7 @@
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
         <v>3.85</v>
@@ -4073,7 +4073,7 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -4100,7 +4100,7 @@
         <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4118,7 +4118,7 @@
         <v>29</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>12</v>
@@ -4172,53 +4172,53 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BC19" t="n">
         <v>3</v>
       </c>
-      <c r="BC19" t="n">
-        <v>2.94</v>
-      </c>
       <c r="BD19" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BF19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG19" t="n">
         <v>2.98</v>
       </c>
-      <c r="BG19" t="n">
-        <v>2.86</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H20" t="n">
         <v>3.05</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
         <v>7</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.02</v>
+        <v>1.81</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.02</v>
+        <v>1.81</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>6.4</v>
@@ -4569,7 +4569,7 @@
         <v>4.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AW21" t="n">
         <v>1.85</v>
@@ -4584,7 +4584,7 @@
         <v>1.81</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
         <v>1.82</v>
@@ -4593,7 +4593,7 @@
         <v>1.81</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BE21" t="n">
         <v>1.85</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
         <v>3.3</v>
@@ -4652,94 +4652,94 @@
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>1.31</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
         <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>500</v>
       </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
@@ -4748,13 +4748,13 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR22" t="n">
         <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>8.6</v>
@@ -4787,20 +4787,20 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>4.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.75</v>
@@ -4882,16 +4882,16 @@
         <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y23" t="n">
         <v>24</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4903,28 +4903,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4945,22 +4945,22 @@
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4972,7 +4972,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
         <v>19.5</v>
@@ -4981,20 +4981,20 @@
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G24" t="n">
         <v>2.86</v>
       </c>
       <c r="H24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I24" t="n">
         <v>2.8</v>
@@ -5088,7 +5088,7 @@
         <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
         <v>12.5</v>
@@ -5097,7 +5097,7 @@
         <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>32</v>
@@ -5121,16 +5121,16 @@
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5166,19 +5166,19 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
         <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5219,55 +5219,55 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G25" t="n">
         <v>1.34</v>
       </c>
       <c r="H25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W25" t="n">
         <v>3.9</v>
@@ -5276,7 +5276,7 @@
         <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,43 +5285,43 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG25" t="n">
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5333,10 +5333,10 @@
         <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>6.2</v>
@@ -5345,10 +5345,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX25" t="n">
         <v>6.4</v>
@@ -5357,13 +5357,13 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB25" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
@@ -5372,17 +5372,17 @@
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="G26" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H26" t="n">
         <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
         <v>3.05</v>
@@ -5443,7 +5443,7 @@
         <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
         <v>2.4</v>
@@ -5458,13 +5458,13 @@
         <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
@@ -5512,7 +5512,7 @@
         <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
         <v>36</v>
@@ -5530,19 +5530,19 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5554,29 +5554,29 @@
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="G27" t="n">
         <v>1.88</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5637,10 +5637,10 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
@@ -5649,7 +5649,7 @@
         <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
         <v>1.92</v>
@@ -5658,10 +5658,10 @@
         <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
         <v>17</v>
@@ -5682,10 +5682,10 @@
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AF27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
         <v>10.5</v>
@@ -5694,7 +5694,7 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -5709,10 +5709,10 @@
         <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AP27" t="n">
         <v>9.6</v>
@@ -5724,7 +5724,7 @@
         <v>16</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5766,11 +5766,11 @@
         <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>6.2</v>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J28" t="n">
         <v>4.5</v>
@@ -5879,7 +5879,7 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
         <v>36</v>
@@ -5924,10 +5924,10 @@
         <v>5.1</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW28" t="n">
         <v>4.2</v>
@@ -5936,10 +5936,10 @@
         <v>5.1</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA28" t="n">
         <v>4.2</v>
@@ -5948,13 +5948,13 @@
         <v>5.7</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BD28" t="n">
         <v>7.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BF28" t="n">
         <v>5.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="G29" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I29" t="n">
         <v>1.7</v>
       </c>
-      <c r="I29" t="n">
-        <v>1.84</v>
-      </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.24</v>
@@ -6019,43 +6019,43 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S29" t="n">
         <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U29" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V29" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6064,13 +6064,13 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF29" t="n">
         <v>1000</v>
@@ -6079,7 +6079,7 @@
         <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6213,16 +6213,16 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
         <v>1.25</v>
@@ -6243,13 +6243,13 @@
         <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y30" t="n">
         <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -6258,10 +6258,10 @@
         <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6294,65 +6294,65 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP30" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT30" t="n">
         <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB30" t="n">
         <v>3.2</v>
       </c>
-      <c r="AX30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ30" t="n">
+      <c r="BC30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
@@ -6395,10 +6395,10 @@
         <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.62</v>
@@ -6407,16 +6407,16 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
         <v>1.17</v>
@@ -6425,10 +6425,10 @@
         <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V31" t="n">
         <v>1.28</v>
@@ -6440,7 +6440,7 @@
         <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>34</v>
@@ -6449,7 +6449,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
@@ -6473,13 +6473,13 @@
         <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="n">
         <v>38</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6497,13 +6497,13 @@
         <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU31" t="n">
         <v>6.4</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
         <v>10.5</v>
@@ -6521,32 +6521,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BD31" t="n">
         <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G32" t="n">
         <v>2.58</v>
@@ -6589,10 +6589,10 @@
         <v>4.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L32" t="n">
         <v>1.49</v>
@@ -6604,13 +6604,13 @@
         <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R32" t="n">
         <v>1.19</v>
@@ -6622,25 +6622,25 @@
         <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X32" t="n">
         <v>9.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
         <v>27</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>8</v>
@@ -6649,28 +6649,28 @@
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG32" t="n">
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI32" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL32" t="n">
         <v>65</v>
@@ -6688,59 +6688,59 @@
         <v>7</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AU32" t="n">
         <v>5.7</v>
       </c>
       <c r="AV32" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
         <v>18.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF32" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G33" t="n">
         <v>2.32</v>
       </c>
       <c r="H33" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="K33" t="n">
         <v>4.8</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU33" t="n">
         <v>1.23</v>
       </c>
-      <c r="AS33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AV33" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="BF33" t="n">
         <v>1.55</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G34" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="H34" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J34" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -6986,22 +6986,22 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q34" t="n">
         <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
         <v>4.3</v>
@@ -7013,10 +7013,10 @@
         <v>1.87</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
@@ -7079,10 +7079,10 @@
         <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="AT34" t="n">
         <v>4.9</v>
@@ -7091,44 +7091,44 @@
         <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="AX34" t="n">
         <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="BB34" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.58</v>
       </c>
       <c r="G35" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H35" t="n">
         <v>4.4</v>
@@ -7174,7 +7174,7 @@
         <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7210,7 +7210,7 @@
         <v>1.16</v>
       </c>
       <c r="W35" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AT35" t="n">
         <v>4.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AX35" t="n">
         <v>5.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="BF35" t="n">
         <v>3.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G36" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J36" t="n">
         <v>3.15</v>
@@ -7377,16 +7377,16 @@
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
         <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R36" t="n">
         <v>1.21</v>
@@ -7398,19 +7398,19 @@
         <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V36" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X36" t="n">
         <v>12</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z36" t="n">
         <v>17.5</v>
@@ -7434,28 +7434,28 @@
         <v>27</v>
       </c>
       <c r="AG36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH36" t="n">
         <v>28</v>
       </c>
       <c r="AI36" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
         <v>90</v>
       </c>
       <c r="AK36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL36" t="n">
         <v>90</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AO36" t="n">
         <v>42</v>
@@ -7470,22 +7470,22 @@
         <v>12.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
         <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AY36" t="n">
         <v>13</v>
@@ -7494,29 +7494,29 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC36" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC36" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD36" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H37" t="n">
         <v>2.48</v>
@@ -7559,10 +7559,10 @@
         <v>3.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7577,7 +7577,7 @@
         <v>1.01</v>
       </c>
       <c r="P37" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q37" t="n">
         <v>1.87</v>
@@ -7616,7 +7616,7 @@
         <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.07</v>
+        <v>1.91</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.07</v>
+        <v>1.91</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.07</v>
+        <v>2.06</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.07</v>
+        <v>2.06</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.07</v>
+        <v>2.04</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.07</v>
+        <v>2.04</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="G38" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="I38" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="J38" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P38" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R38" t="n">
         <v>1.2</v>
@@ -7783,52 +7783,52 @@
         <v>1.01</v>
       </c>
       <c r="T38" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="U38" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="V38" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AB38" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
         <v>13</v>
       </c>
       <c r="AE38" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG38" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AH38" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7846,65 +7846,65 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX38" t="n">
         <v>4.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AZ38" t="n">
         <v>4</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -760,22 +760,22 @@
         <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -784,31 +784,31 @@
         <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>26</v>
@@ -835,92 +835,92 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR2" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>2.52</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,13 +981,13 @@
         <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S3" t="n">
         <v>1.05</v>
@@ -1002,7 +1002,7 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
@@ -1375,10 +1375,10 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1390,7 +1390,7 @@
         <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,7 +1563,7 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
         <v>1.7</v>
@@ -1572,10 +1572,10 @@
         <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
@@ -1590,7 +1590,7 @@
         <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
         <v>220</v>
@@ -1602,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1611,7 +1611,7 @@
         <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
         <v>9.6</v>
@@ -1650,13 +1650,13 @@
         <v>42</v>
       </c>
       <c r="AS6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>19.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1927,16 +1927,16 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W8" t="n">
         <v>1.18</v>
@@ -2035,7 +2035,7 @@
         <v>1.17</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AS8" t="n">
         <v>1.2</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
         <v>3.8</v>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
@@ -2157,16 +2157,16 @@
         <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
         <v>5.5</v>
@@ -2423,7 +2423,7 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
         <v>7.8</v>
@@ -2459,7 +2459,7 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE10" t="n">
         <v>7.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I11" t="n">
         <v>3.2</v>
@@ -2551,7 +2551,7 @@
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
         <v>1.55</v>
@@ -2635,7 +2635,7 @@
         <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY11" t="n">
         <v>7</v>
@@ -2647,7 +2647,7 @@
         <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
         <v>5.6</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BF11" t="n">
         <v>5.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
         <v>2.62</v>
@@ -2712,7 +2712,7 @@
         <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>1.36</v>
@@ -2721,34 +2721,34 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
         <v>26</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -2823,44 +2823,44 @@
         <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>1.93</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -2939,13 +2939,13 @@
         <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W13" t="n">
         <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -2954,16 +2954,16 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2972,7 +2972,7 @@
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
         <v>60</v>
@@ -3008,10 +3008,10 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>5.9</v>
@@ -3023,38 +3023,38 @@
         <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
         <v>2.96</v>
@@ -3097,13 +3097,13 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3175,7 +3175,7 @@
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="n">
         <v>110</v>
@@ -3187,10 +3187,10 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
         <v>5.8</v>
@@ -3199,10 +3199,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -3214,31 +3214,31 @@
         <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY14" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
         <v>27</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
         <v>6.8</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3297,22 +3297,22 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -3321,19 +3321,19 @@
         <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3348,7 +3348,7 @@
         <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3360,7 +3360,7 @@
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -3387,31 +3387,31 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>7.8</v>
@@ -3420,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3429,10 +3429,10 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
         <v>4.9</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -3626,7 +3626,7 @@
         <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G17" t="n">
         <v>1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
         <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.49</v>
@@ -3715,7 +3715,7 @@
         <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
         <v>2.24</v>
@@ -3748,7 +3748,7 @@
         <v>10</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>28</v>
@@ -3781,10 +3781,10 @@
         <v>13.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
         <v>5.7</v>
@@ -3796,7 +3796,7 @@
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3817,20 +3817,20 @@
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
         <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -3888,10 +3888,10 @@
         <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
         <v>1.92</v>
@@ -3915,7 +3915,7 @@
         <v>2.32</v>
       </c>
       <c r="X18" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
         <v>1000</v>
@@ -3945,7 +3945,7 @@
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3954,7 +3954,7 @@
         <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3975,10 +3975,10 @@
         <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
@@ -4002,7 +4002,7 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4014,17 +4014,17 @@
         <v>19.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
         <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4085,19 +4085,19 @@
         <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
         <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
         <v>1.72</v>
@@ -4205,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BE19" t="n">
         <v>3.05</v>
@@ -4214,11 +4214,11 @@
         <v>3.05</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
         <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.22</v>
@@ -4384,7 +4384,7 @@
         <v>5.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.75</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G21" t="n">
         <v>2.08</v>
@@ -4461,19 +4461,19 @@
         <v>6.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
         <v>2.04</v>
@@ -4485,7 +4485,7 @@
         <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
         <v>1.94</v>
@@ -4575,7 +4575,7 @@
         <v>1.85</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.73</v>
+        <v>5.6</v>
       </c>
       <c r="AY21" t="n">
         <v>1.69</v>
@@ -4593,7 +4593,7 @@
         <v>1.81</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BE21" t="n">
         <v>1.85</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4685,10 +4685,10 @@
         <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>22</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
         <v>2.18</v>
@@ -4855,16 +4855,16 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
         <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
@@ -4873,16 +4873,16 @@
         <v>3.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
         <v>19.5</v>
@@ -4948,7 +4948,7 @@
         <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>7.2</v>
@@ -4960,7 +4960,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4972,7 +4972,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
         <v>19.5</v>
@@ -4981,10 +4981,10 @@
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
         <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>500</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>29</v>
+        <v>5.4</v>
       </c>
       <c r="AT24" t="n">
         <v>9.800000000000001</v>
@@ -5169,16 +5169,16 @@
         <v>5.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>5.5</v>
       </c>
       <c r="BC24" t="n">
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>29</v>
+        <v>5.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J25" t="n">
         <v>5.3</v>
@@ -5261,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
         <v>1.62</v>
@@ -5291,7 +5291,7 @@
         <v>14</v>
       </c>
       <c r="AD25" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5303,7 +5303,7 @@
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5333,13 +5333,13 @@
         <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
@@ -5354,10 +5354,10 @@
         <v>6.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BA25" t="n">
         <v>9.800000000000001</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.58</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="n">
         <v>3.35</v>
@@ -5464,7 +5464,7 @@
         <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>5.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
@@ -5625,7 +5625,7 @@
         <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>1.47</v>
       </c>
       <c r="G28" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
         <v>5.8</v>
@@ -5831,7 +5831,7 @@
         <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
         <v>1.63</v>
@@ -5852,7 +5852,7 @@
         <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5945,16 +5945,16 @@
         <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BF28" t="n">
         <v>5.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="H29" t="n">
         <v>1.65</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J29" t="n">
         <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.24</v>
@@ -6025,13 +6025,13 @@
         <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q29" t="n">
         <v>1.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
         <v>2.3</v>
@@ -6043,10 +6043,10 @@
         <v>2.32</v>
       </c>
       <c r="V29" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
         <v>90</v>
@@ -6103,7 +6103,7 @@
         <v>6.6</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -6127,7 +6127,7 @@
         <v>8.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6148,17 +6148,17 @@
         <v>7.4</v>
       </c>
       <c r="BE29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF29" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG29" t="n">
         <v>5.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
         <v>4.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>4.8</v>
@@ -6330,7 +6330,7 @@
         <v>5.1</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
         <v>3.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>3.05</v>
@@ -6407,7 +6407,7 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
         <v>1.6</v>
@@ -6542,11 +6542,11 @@
         <v>5.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
@@ -6628,7 +6628,7 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X32" t="n">
         <v>9.4</v>
@@ -6658,7 +6658,7 @@
         <v>14.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>24</v>
@@ -6682,7 +6682,7 @@
         <v>36</v>
       </c>
       <c r="AO32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP32" t="n">
         <v>7</v>
@@ -6694,10 +6694,10 @@
         <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
         <v>5.7</v>
@@ -6706,7 +6706,7 @@
         <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6718,29 +6718,29 @@
         <v>18.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF32" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE32" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG32" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.86</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="H33" t="n">
         <v>3.95</v>
@@ -6822,7 +6822,7 @@
         <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6974,43 +6974,43 @@
         <v>2.72</v>
       </c>
       <c r="I34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>2.8</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.01</v>
       </c>
-      <c r="M34" t="n">
-        <v>1.05</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O34" t="n">
         <v>1.27</v>
       </c>
       <c r="P34" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
         <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
         <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U34" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V34" t="n">
         <v>1.45</v>
@@ -7079,10 +7079,10 @@
         <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="AT34" t="n">
         <v>4.9</v>
@@ -7091,44 +7091,44 @@
         <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AX34" t="n">
         <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="BB34" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7177,13 +7177,13 @@
         <v>7.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.71</v>
+        <v>2.78</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
@@ -7195,16 +7195,16 @@
         <v>1.86</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>1.86</v>
+        <v>2.72</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.16</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AT35" t="n">
         <v>4.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AX35" t="n">
         <v>5.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.4</v>
       </c>
-      <c r="BA35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BC35" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BF35" t="n">
         <v>3.8</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
         <v>3.1</v>
       </c>
       <c r="K37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7574,7 +7574,7 @@
         <v>2.86</v>
       </c>
       <c r="O37" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P37" t="n">
         <v>1.76</v>
@@ -7583,16 +7583,16 @@
         <v>1.87</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
         <v>1.37</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G38" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I38" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J38" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K38" t="n">
         <v>3.65</v>
@@ -7762,37 +7762,37 @@
         <v>1.45</v>
       </c>
       <c r="M38" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O38" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P38" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R38" t="n">
         <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V38" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W38" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -7819,13 +7819,13 @@
         <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
         <v>27</v>
       </c>
       <c r="AH38" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>26</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY38" t="n">
         <v>4</v>
       </c>
-      <c r="AX38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC38" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC38" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8132,19 +8132,19 @@
         <v>2.02</v>
       </c>
       <c r="G40" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I40" t="n">
         <v>4.9</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>3.1</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
         <v>1.47</v>
@@ -8180,13 +8180,13 @@
         <v>1.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
         <v>1000</v>
@@ -8195,22 +8195,22 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
         <v>1000</v>
@@ -8219,7 +8219,7 @@
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
         <v>1000</v>
@@ -8237,16 +8237,16 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AQ40" t="n">
         <v>10</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -8255,10 +8255,10 @@
         <v>6.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AX40" t="n">
         <v>9.800000000000001</v>
@@ -8267,32 +8267,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF40" t="n">
         <v>18</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
         <v>1.17</v>
@@ -769,19 +769,19 @@
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
@@ -790,22 +790,22 @@
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S2" t="n">
         <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
         <v>6.8</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -850,7 +850,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,7 +859,7 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -871,22 +871,22 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU2" t="n">
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
         <v>6.6</v>
@@ -895,32 +895,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="J3" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
         <v>2.24</v>
@@ -1154,37 +1154,37 @@
         <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
@@ -1193,22 +1193,22 @@
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
         <v>15</v>
@@ -1217,10 +1217,10 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF4" t="n">
         <v>18.5</v>
@@ -1229,7 +1229,7 @@
         <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
@@ -1244,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>14.5</v>
@@ -1262,7 +1262,7 @@
         <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1286,7 +1286,7 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC5" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1429,10 +1429,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.87</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.92</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.74</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.92</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.88</v>
+        <v>2.76</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.96</v>
+        <v>2.98</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.93</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1533,130 +1533,130 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR6" t="n">
         <v>42</v>
       </c>
       <c r="AS6" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
         <v>19.5</v>
@@ -1674,10 +1674,10 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1689,14 +1689,14 @@
         <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,34 +1751,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>1.18</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J8" t="n">
         <v>2.68</v>
@@ -1945,31 +1945,31 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
         <v>1.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
         <v>1.18</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2154,7 +2154,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2166,7 +2166,7 @@
         <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AT9" t="n">
         <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="BF9" t="n">
         <v>1.32</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
         <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
         <v>5.5</v>
@@ -2327,37 +2327,37 @@
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
         <v>2.24</v>
@@ -2378,13 +2378,13 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2405,74 +2405,74 @@
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>8.4</v>
       </c>
       <c r="AS10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW10" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG10" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>2.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
@@ -2527,7 +2527,7 @@
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>1.3</v>
@@ -2542,7 +2542,7 @@
         <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T11" t="n">
         <v>1.7</v>
@@ -2629,13 +2629,13 @@
         <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AY11" t="n">
         <v>7</v>
@@ -2647,7 +2647,7 @@
         <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
         <v>5.6</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BF11" t="n">
         <v>5.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J12" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>26</v>
@@ -2766,7 +2766,7 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -2823,44 +2823,44 @@
         <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -2909,7 +2909,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2918,7 +2918,7 @@
         <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
         <v>1.91</v>
@@ -2933,16 +2933,16 @@
         <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2975,7 +2975,7 @@
         <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3023,38 +3023,38 @@
         <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G14" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H14" t="n">
         <v>2.8</v>
@@ -3097,52 +3097,52 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
         <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
@@ -3151,7 +3151,7 @@
         <v>130</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
@@ -3175,10 +3175,10 @@
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3199,56 +3199,56 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I15" t="n">
         <v>10.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="X15" t="n">
         <v>90</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC15" t="n">
         <v>42</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="AK15" t="n">
         <v>65</v>
@@ -3387,25 +3387,25 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="n">
         <v>4.2</v>
@@ -3414,13 +3414,13 @@
         <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3429,10 +3429,10 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3473,52 +3473,52 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
         <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R16" t="n">
         <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
         <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -3545,16 +3545,16 @@
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AE16" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
         <v>26</v>
@@ -3578,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
         <v>9.199999999999999</v>
@@ -3590,7 +3590,7 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -3614,7 +3614,7 @@
         <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
@@ -3623,20 +3623,20 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3667,100 +3667,100 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y17" t="n">
         <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC17" t="n">
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>480</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
         <v>55</v>
@@ -3769,46 +3769,46 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3817,20 +3817,20 @@
         <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G18" t="n">
         <v>1.76</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
@@ -3879,28 +3879,28 @@
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
@@ -3909,10 +3909,10 @@
         <v>1.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>90</v>
@@ -3930,7 +3930,7 @@
         <v>13.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3945,7 +3945,7 @@
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3975,13 +3975,13 @@
         <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
@@ -4002,7 +4002,7 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -4014,17 +4014,17 @@
         <v>19.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4055,49 +4055,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P19" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
         <v>1.72</v>
@@ -4109,22 +4109,22 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y19" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>13</v>
-      </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>20</v>
@@ -4163,7 +4163,7 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.2</v>
+        <v>2.54</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.2</v>
@@ -4172,53 +4172,53 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4249,55 +4249,55 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="G20" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.18</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -4351,7 +4351,7 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -4360,13 +4360,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AT20" t="n">
         <v>4.4</v>
@@ -4375,10 +4375,10 @@
         <v>4.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AX20" t="n">
         <v>5.1</v>
@@ -4387,32 +4387,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
         <v>3.85</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="H21" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -4497,7 +4497,7 @@
         <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4551,16 +4551,16 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AT21" t="n">
         <v>4.4</v>
@@ -4569,44 +4569,44 @@
         <v>4.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AX21" t="n">
         <v>5.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AZ21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.81</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.85</v>
       </c>
       <c r="BF21" t="n">
         <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
         <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
         <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>22</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="n">
         <v>65</v>
@@ -4754,19 +4754,19 @@
         <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
         <v>8.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
@@ -4778,10 +4778,10 @@
         <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>18.5</v>
@@ -4790,17 +4790,17 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
         <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X23" t="n">
         <v>19.5</v>
@@ -4900,7 +4900,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
         <v>34</v>
@@ -4924,7 +4924,7 @@
         <v>110</v>
       </c>
       <c r="AK23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4948,7 +4948,7 @@
         <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT23" t="n">
         <v>7.2</v>
@@ -4960,7 +4960,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4972,7 +4972,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB23" t="n">
         <v>19.5</v>
@@ -4981,20 +4981,20 @@
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5025,64 +5025,64 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H24" t="n">
         <v>2.56</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.89</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
         <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X24" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z24" t="n">
         <v>22</v>
@@ -5091,16 +5091,16 @@
         <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="n">
         <v>19.5</v>
@@ -5112,7 +5112,7 @@
         <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
@@ -5130,7 +5130,7 @@
         <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>9.800000000000001</v>
@@ -5166,19 +5166,19 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC24" t="n">
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5219,46 +5219,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
         <v>15</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -5270,7 +5270,7 @@
         <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X25" t="n">
         <v>21</v>
@@ -5303,7 +5303,7 @@
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5419,40 +5419,40 @@
         <v>2.66</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>3.05</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T26" t="n">
         <v>1.98</v>
@@ -5467,25 +5467,25 @@
         <v>1.6</v>
       </c>
       <c r="X26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>11</v>
-      </c>
       <c r="Z26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>55</v>
@@ -5509,31 +5509,31 @@
         <v>38</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR26" t="n">
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
@@ -5542,41 +5542,41 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H27" t="n">
         <v>5.1</v>
@@ -5622,22 +5622,22 @@
         <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
         <v>2.14</v>
@@ -5646,25 +5646,25 @@
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
         <v>1.91</v>
       </c>
       <c r="U27" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X27" t="n">
         <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
         <v>48</v>
@@ -5709,22 +5709,22 @@
         <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>410</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -5739,7 +5739,7 @@
         <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>8.6</v>
@@ -5757,10 +5757,10 @@
         <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
         <v>10</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
         <v>1.55</v>
@@ -5810,37 +5810,37 @@
         <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T28" t="n">
         <v>1.9</v>
@@ -5849,16 +5849,16 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z28" t="n">
         <v>1000</v>
@@ -5867,7 +5867,7 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
         <v>42</v>
@@ -5882,7 +5882,7 @@
         <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5915,7 +5915,7 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
@@ -5927,13 +5927,13 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW28" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW28" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX28" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>5.8</v>
@@ -5945,26 +5945,26 @@
         <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
         <v>5.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -5995,67 +5995,67 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="G29" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
         <v>1.65</v>
       </c>
       <c r="I29" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="J29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P29" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R29" t="n">
         <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U29" t="n">
         <v>2.32</v>
       </c>
       <c r="V29" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
         <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Z29" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV29" t="n">
         <v>8.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF29" t="n">
         <v>9</v>
       </c>
-      <c r="BA29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG29" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="n">
         <v>1.84</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
         <v>1.69</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V30" t="n">
         <v>2.02</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V30" t="n">
-        <v>2</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
         <v>90</v>
@@ -6300,59 +6300,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT30" t="n">
         <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AY30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.8</v>
       </c>
-      <c r="AZ30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G31" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
         <v>4.5</v>
@@ -6398,7 +6398,7 @@
         <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L31" t="n">
         <v>1.62</v>
@@ -6407,13 +6407,13 @@
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>1.6</v>
       </c>
       <c r="P31" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q31" t="n">
         <v>2.8</v>
@@ -6443,7 +6443,7 @@
         <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6473,13 +6473,13 @@
         <v>120</v>
       </c>
       <c r="AJ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL31" t="n">
         <v>75</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>460</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6500,7 +6500,7 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT31" t="n">
         <v>5.9</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX31" t="n">
         <v>10.5</v>
@@ -6524,7 +6524,7 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB31" t="n">
         <v>13</v>
@@ -6536,17 +6536,17 @@
         <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF31" t="n">
         <v>5.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -6577,46 +6577,46 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
         <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P32" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R32" t="n">
         <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6625,16 +6625,16 @@
         <v>1.78</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X32" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>27</v>
@@ -6643,19 +6643,19 @@
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE32" t="n">
         <v>65</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
         <v>12.5</v>
@@ -6667,10 +6667,10 @@
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK32" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL32" t="n">
         <v>65</v>
@@ -6679,68 +6679,68 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>95</v>
       </c>
       <c r="AP32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF32" t="n">
         <v>8</v>
       </c>
-      <c r="BB32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -6771,58 +6771,58 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I33" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="O33" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR33" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AS33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>1.33</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="BA33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC33" t="n">
         <v>1.33</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="BD33" t="n">
         <v>1.35</v>
       </c>
-      <c r="AT33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BE33" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BF33" t="n">
         <v>1.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.55</v>
+        <v>16.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="G34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H34" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K34" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q34" t="n">
         <v>2.48</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.22</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T34" t="n">
         <v>1.94</v>
@@ -7013,7 +7013,7 @@
         <v>1.9</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.46</v>
@@ -7079,7 +7079,7 @@
         <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS34" t="n">
         <v>2.52</v>
@@ -7091,7 +7091,7 @@
         <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW34" t="n">
         <v>2.5</v>
@@ -7100,35 +7100,35 @@
         <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD34" t="n">
         <v>2.54</v>
       </c>
-      <c r="BA34" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE34" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -7159,58 +7159,58 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="H35" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7261,7 +7261,7 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -7356,28 +7356,28 @@
         <v>3.45</v>
       </c>
       <c r="G36" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I36" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
         <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M36" t="n">
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="O36" t="n">
         <v>1.5</v>
@@ -7386,31 +7386,31 @@
         <v>1.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R36" t="n">
         <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
         <v>1.83</v>
       </c>
       <c r="V36" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X36" t="n">
         <v>12</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z36" t="n">
         <v>17.5</v>
@@ -7440,13 +7440,13 @@
         <v>28</v>
       </c>
       <c r="AI36" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AJ36" t="n">
         <v>90</v>
       </c>
       <c r="AK36" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL36" t="n">
         <v>90</v>
@@ -7455,10 +7455,10 @@
         <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AP36" t="n">
         <v>8.6</v>
@@ -7467,7 +7467,7 @@
         <v>6.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS36" t="n">
         <v>14.5</v>
@@ -7485,38 +7485,38 @@
         <v>14.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ36" t="n">
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG36" t="n">
         <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -7547,61 +7547,61 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="H37" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" t="n">
         <v>3.7</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>7</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.86</v>
       </c>
       <c r="O37" t="n">
         <v>1.31</v>
       </c>
       <c r="P37" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R37" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W37" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y37" t="n">
         <v>1000</v>
@@ -7616,7 +7616,7 @@
         <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="AD37" t="n">
         <v>1000</v>
@@ -7631,13 +7631,13 @@
         <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.93</v>
+        <v>7</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.91</v>
+        <v>6.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="AU37" t="n">
         <v>4.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.06</v>
+        <v>5.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -7741,94 +7741,94 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="H38" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="I38" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="J38" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M38" t="n">
         <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V38" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y38" t="n">
         <v>7.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB38" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AC38" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG38" t="n">
         <v>27</v>
       </c>
       <c r="AH38" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7846,13 +7846,13 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AR38" t="n">
         <v>7.8</v>
@@ -7861,16 +7861,16 @@
         <v>16.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AU38" t="n">
         <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.1</v>
+        <v>19</v>
       </c>
       <c r="AX38" t="n">
         <v>4.4</v>
@@ -7879,7 +7879,7 @@
         <v>4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BA38" t="n">
         <v>4.5</v>
@@ -7888,10 +7888,10 @@
         <v>4.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE38" t="n">
         <v>4.6</v>
@@ -7900,11 +7900,11 @@
         <v>4.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -7935,46 +7935,46 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -7983,52 +7983,52 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL39" t="n">
         <v>1000</v>
@@ -8037,7 +8037,7 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
@@ -8091,14 +8091,14 @@
         <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG39" t="n">
         <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>
@@ -8129,46 +8129,46 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G40" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K40" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O40" t="n">
         <v>1.5</v>
       </c>
       <c r="P40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R40" t="n">
         <v>1.21</v>
       </c>
       <c r="S40" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T40" t="n">
         <v>2.06</v>
@@ -8177,10 +8177,10 @@
         <v>1.77</v>
       </c>
       <c r="V40" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W40" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X40" t="n">
         <v>10.5</v>
@@ -8201,7 +8201,7 @@
         <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
@@ -8237,16 +8237,16 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ40" t="n">
         <v>10</v>
       </c>
       <c r="AR40" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS40" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -8255,10 +8255,10 @@
         <v>6.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX40" t="n">
         <v>9.800000000000001</v>
@@ -8270,29 +8270,29 @@
         <v>19</v>
       </c>
       <c r="BA40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD40" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE40" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF40" t="n">
         <v>18</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 00:54:25</t>
+          <t>2026-03-27 03:07:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -763,16 +763,16 @@
         <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -787,13 +787,13 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
         <v>2.2</v>
@@ -802,7 +802,7 @@
         <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -883,7 +883,7 @@
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
         <v>4.2</v>
@@ -895,7 +895,7 @@
         <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
@@ -907,20 +907,20 @@
         <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="I3" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
         <v>23</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AK3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
         <v>150</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT3" t="n">
         <v>5.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
         <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
         <v>38</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB4" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
         <v>1.38</v>
@@ -1351,7 +1351,7 @@
         <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
         <v>7.8</v>
@@ -1360,7 +1360,7 @@
         <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>4.7</v>
@@ -1387,7 +1387,7 @@
         <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
         <v>3.6</v>
@@ -1450,7 +1450,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1459,13 +1459,13 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1477,22 +1477,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.76</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BF5" t="n">
         <v>2.98</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1533,52 +1533,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
         <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
         <v>1.19</v>
@@ -1590,19 +1590,19 @@
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1620,10 +1620,10 @@
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
@@ -1632,16 +1632,16 @@
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>22</v>
@@ -1650,19 +1650,19 @@
         <v>42</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -1677,26 +1677,26 @@
         <v>55</v>
       </c>
       <c r="BB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC6" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE6" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>310</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.85</v>
       </c>
-      <c r="K7" t="n">
-        <v>85</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V8" t="n">
         <v>2.4</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.65</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF8" t="n">
         <v>500</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG8" t="n">
         <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.19</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.17</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.2</v>
+        <v>19.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.18</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.2</v>
+        <v>13.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.18</v>
+        <v>19.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.55</v>
+        <v>9.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="I9" t="n">
-        <v>310</v>
+        <v>13.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.45</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.45</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.32</v>
+        <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2327,43 +2327,43 @@
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.24</v>
-      </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>21</v>
@@ -2372,10 +2372,10 @@
         <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2393,10 +2393,10 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>19</v>
@@ -2408,71 +2408,71 @@
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10" t="n">
         <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
         <v>8</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2503,97 +2503,97 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
         <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>3.85</v>
       </c>
       <c r="BF11" t="n">
         <v>5.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.44</v>
@@ -2721,16 +2721,16 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
         <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
@@ -2745,7 +2745,7 @@
         <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.51</v>
@@ -2754,16 +2754,16 @@
         <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
         <v>42</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS12" t="n">
         <v>6.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BA12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BB12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BD12" t="n">
         <v>6.2</v>
       </c>
-      <c r="BD12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -2909,22 +2909,22 @@
         <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
         <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
@@ -2939,13 +2939,13 @@
         <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -3008,7 +3008,7 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3023,38 +3023,38 @@
         <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.4</v>
@@ -3109,7 +3109,7 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>1.42</v>
@@ -3130,10 +3130,10 @@
         <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
@@ -3175,13 +3175,13 @@
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3202,19 +3202,19 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>7.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
         <v>8.4</v>
@@ -3229,7 +3229,7 @@
         <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
         <v>16</v>
@@ -3238,17 +3238,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
         <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
         <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I15" t="n">
         <v>10.5</v>
@@ -3321,16 +3321,16 @@
         <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
         <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X15" t="n">
         <v>90</v>
@@ -3348,7 +3348,7 @@
         <v>6.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3393,19 +3393,19 @@
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW15" t="n">
         <v>4.2</v>
@@ -3426,13 +3426,13 @@
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
         <v>5.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
@@ -3497,22 +3497,22 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
         <v>1.92</v>
@@ -3530,16 +3530,16 @@
         <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -3557,10 +3557,10 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AJ16" t="n">
         <v>25</v>
@@ -3572,7 +3572,7 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
@@ -3590,53 +3590,53 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H17" t="n">
         <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -3685,13 +3685,13 @@
         <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -3700,19 +3700,19 @@
         <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
         <v>1.2</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK17" t="n">
         <v>24</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.41</v>
@@ -3885,40 +3885,40 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
         <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,25 +3972,25 @@
         <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
@@ -3999,32 +3999,32 @@
         <v>7.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4058,31 +4058,31 @@
         <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P19" t="n">
         <v>1.57</v>
@@ -4094,131 +4094,131 @@
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AW19" t="n">
-        <v>2.86</v>
+        <v>9.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.52</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.84</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.88</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.84</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.88</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.86</v>
+        <v>9.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
         <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
@@ -4273,7 +4273,7 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.39</v>
@@ -4291,128 +4291,128 @@
         <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.54</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.54</v>
+        <v>7.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.54</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF20" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="G21" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -4467,37 +4467,37 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4509,22 +4509,22 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>95</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH21" t="n">
         <v>1000</v>
@@ -4533,80 +4533,80 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.78</v>
+        <v>9.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.76</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.77</v>
+        <v>10.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.76</v>
+        <v>17</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.79</v>
+        <v>10</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4637,61 +4637,61 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
         <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.55</v>
       </c>
       <c r="K22" t="n">
         <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
         <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
         <v>22</v>
@@ -4703,19 +4703,19 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4724,7 +4724,7 @@
         <v>36</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>75</v>
@@ -4742,10 +4742,10 @@
         <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.6</v>
@@ -4754,10 +4754,10 @@
         <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -4766,41 +4766,41 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
         <v>1.47</v>
@@ -4855,34 +4855,34 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
         <v>2.18</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
         <v>19.5</v>
@@ -4891,13 +4891,13 @@
         <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
         <v>9</v>
       </c>
       <c r="AX23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE23" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF23" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5025,52 +5025,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G24" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
         <v>1.58</v>
@@ -5079,19 +5079,19 @@
         <v>1.54</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
         <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
@@ -5109,13 +5109,13 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>150</v>
       </c>
       <c r="AJ24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK24" t="n">
         <v>32</v>
@@ -5130,19 +5130,19 @@
         <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
         <v>9.800000000000001</v>
@@ -5163,32 +5163,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
         <v>7.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
         <v>1.33</v>
@@ -5228,10 +5228,10 @@
         <v>13</v>
       </c>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
@@ -5264,7 +5264,7 @@
         <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
         <v>1.07</v>
@@ -5276,7 +5276,7 @@
         <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5288,10 +5288,10 @@
         <v>7.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5327,13 +5327,13 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
@@ -5342,7 +5342,7 @@
         <v>6.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
         <v>8.6</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>2.58</v>
       </c>
       <c r="G26" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
         <v>3.05</v>
@@ -5431,31 +5431,31 @@
         <v>3.25</v>
       </c>
       <c r="L26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
         <v>1.9</v>
@@ -5464,16 +5464,16 @@
         <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y26" t="n">
         <v>10</v>
       </c>
-      <c r="Y26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
         <v>150</v>
@@ -5488,7 +5488,7 @@
         <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="n">
         <v>16.5</v>
@@ -5500,13 +5500,13 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
         <v>60</v>
@@ -5521,19 +5521,19 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
@@ -5542,7 +5542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5554,7 +5554,7 @@
         <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
@@ -5563,10 +5563,10 @@
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>1.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
@@ -5634,7 +5634,7 @@
         <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
         <v>1.8</v>
@@ -5646,16 +5646,16 @@
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
         <v>2.16</v>
@@ -5664,7 +5664,7 @@
         <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
         <v>48</v>
@@ -5679,13 +5679,13 @@
         <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>160</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG27" t="n">
         <v>10.5</v>
@@ -5709,13 +5709,13 @@
         <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO27" t="n">
         <v>410</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>14</v>
@@ -5733,13 +5733,13 @@
         <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW27" t="n">
         <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
         <v>8.6</v>
@@ -5760,17 +5760,17 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H28" t="n">
         <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
         <v>1.35</v>
@@ -5828,10 +5828,10 @@
         <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
         <v>1.74</v>
@@ -5840,7 +5840,7 @@
         <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T28" t="n">
         <v>1.9</v>
@@ -5852,7 +5852,7 @@
         <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5867,10 +5867,10 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AD28" t="n">
         <v>1000</v>
@@ -5879,10 +5879,10 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5891,7 +5891,7 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>1000</v>
@@ -5915,25 +5915,25 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
         <v>7.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AY28" t="n">
         <v>5.8</v>
@@ -5942,29 +5942,29 @@
         <v>11.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="I29" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
         <v>4.8</v>
@@ -6022,37 +6022,37 @@
         <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S29" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U29" t="n">
         <v>2.32</v>
       </c>
       <c r="V29" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="n">
         <v>25</v>
@@ -6064,10 +6064,10 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AE29" t="n">
         <v>29</v>
@@ -6079,7 +6079,7 @@
         <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6100,10 +6100,10 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>7</v>
@@ -6121,44 +6121,44 @@
         <v>5.9</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW29" t="n">
         <v>8.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
         <v>14.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H30" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="I30" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.49</v>
@@ -6216,10 +6216,10 @@
         <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
         <v>2.28</v>
@@ -6231,16 +6231,16 @@
         <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U30" t="n">
         <v>1.83</v>
       </c>
       <c r="V30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X30" t="n">
         <v>90</v>
@@ -6255,13 +6255,13 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC30" t="n">
         <v>14</v>
       </c>
       <c r="AD30" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6273,7 +6273,7 @@
         <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>55</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV30" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU30" t="n">
+      <c r="AW30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BC30" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD30" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="BF30" t="n">
         <v>3</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L31" t="n">
         <v>1.62</v>
@@ -6455,13 +6455,13 @@
         <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
         <v>13.5</v>
@@ -6476,31 +6476,31 @@
         <v>32</v>
       </c>
       <c r="AK31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
         <v>34</v>
       </c>
-      <c r="AL31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
         <v>5.9</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX31" t="n">
         <v>10.5</v>
@@ -6521,32 +6521,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BB31" t="n">
         <v>13</v>
       </c>
       <c r="BC31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>50</v>
       </c>
       <c r="BE31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG31" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6577,170 +6577,170 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G32" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="V32" t="n">
         <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY32" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y32" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="AZ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD32" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ32" t="n">
+      <c r="BE32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF32" t="n">
         <v>19</v>
       </c>
-      <c r="BA32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>8</v>
-      </c>
       <c r="BG32" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6777,19 +6777,19 @@
         <v>2.12</v>
       </c>
       <c r="H33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
         <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
         <v>1.12</v>
@@ -6813,19 +6813,19 @@
         <v>5.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W33" t="n">
         <v>1.89</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
@@ -6837,10 +6837,10 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
@@ -6849,10 +6849,10 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AH33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.36</v>
+        <v>5.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.36</v>
+        <v>10</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.24</v>
+        <v>4.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.36</v>
+        <v>28</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.32</v>
+        <v>5.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.36</v>
+        <v>9.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.35</v>
+        <v>3.05</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>16.5</v>
+        <v>3.15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6968,49 +6968,49 @@
         <v>2.88</v>
       </c>
       <c r="G34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H34" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J34" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K34" t="n">
         <v>3.15</v>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U34" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="n">
         <v>1.5</v>
@@ -7019,7 +7019,7 @@
         <v>1.46</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="n">
         <v>20</v>
@@ -7079,10 +7079,10 @@
         <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AT34" t="n">
         <v>4.9</v>
@@ -7091,44 +7091,44 @@
         <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AX34" t="n">
         <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD34" t="n">
         <v>2.48</v>
       </c>
-      <c r="BA34" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BE34" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BF34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7159,46 +7159,46 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I35" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L35" t="n">
         <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
         <v>3.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
         <v>1.94</v>
@@ -7210,10 +7210,10 @@
         <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
@@ -7225,10 +7225,10 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7237,10 +7237,10 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH35" t="n">
         <v>1000</v>
@@ -7249,13 +7249,13 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.42</v>
+        <v>6.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.44</v>
+        <v>6.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="AT35" t="n">
         <v>4.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.39</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.44</v>
+        <v>5.9</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="AX35" t="n">
         <v>5.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.41</v>
+        <v>5.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.41</v>
+        <v>5.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.43</v>
+        <v>6.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.55</v>
+        <v>2.78</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G36" t="n">
         <v>3.75</v>
@@ -7371,7 +7371,7 @@
         <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
         <v>1.11</v>
@@ -7401,7 +7401,7 @@
         <v>1.83</v>
       </c>
       <c r="V36" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W36" t="n">
         <v>1.37</v>
@@ -7413,7 +7413,7 @@
         <v>7.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA36" t="n">
         <v>44</v>
@@ -7425,19 +7425,19 @@
         <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG36" t="n">
         <v>18</v>
       </c>
       <c r="AH36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI36" t="n">
         <v>370</v>
@@ -7446,7 +7446,7 @@
         <v>90</v>
       </c>
       <c r="AK36" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AL36" t="n">
         <v>90</v>
@@ -7494,29 +7494,29 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BG36" t="n">
         <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G37" t="n">
         <v>2.78</v>
@@ -7556,13 +7556,13 @@
         <v>2.8</v>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L37" t="n">
         <v>1.4</v>
@@ -7589,7 +7589,7 @@
         <v>3.35</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U37" t="n">
         <v>2.14</v>
@@ -7601,7 +7601,7 @@
         <v>1.56</v>
       </c>
       <c r="X37" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="Y37" t="n">
         <v>1000</v>
@@ -7613,13 +7613,13 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC37" t="n">
         <v>14</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
@@ -7631,7 +7631,7 @@
         <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI37" t="n">
         <v>500</v>
@@ -7664,7 +7664,7 @@
         <v>7.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="AT37" t="n">
         <v>6.2</v>
@@ -7676,7 +7676,7 @@
         <v>7.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX37" t="n">
         <v>6.8</v>
@@ -7688,19 +7688,19 @@
         <v>6.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BF37" t="n">
         <v>6</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>5.4</v>
       </c>
       <c r="G38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I38" t="n">
         <v>1.91</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
         <v>3.85</v>
@@ -7762,37 +7762,37 @@
         <v>1.47</v>
       </c>
       <c r="M38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U38" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V38" t="n">
         <v>2.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X38" t="n">
         <v>13.5</v>
@@ -7825,10 +7825,10 @@
         <v>27</v>
       </c>
       <c r="AH38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7846,65 +7846,65 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.98</v>
+        <v>6</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS38" t="n">
         <v>16.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU38" t="n">
         <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY38" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ38" t="n">
         <v>17</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G39" t="n">
         <v>2.46</v>
@@ -7944,7 +7944,7 @@
         <v>3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J39" t="n">
         <v>3.05</v>
@@ -7965,25 +7965,25 @@
         <v>1.51</v>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q39" t="n">
         <v>2.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
         <v>5.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
         <v>1.68</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
         <v>3.15</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L40" t="n">
         <v>1.55</v>
@@ -8153,7 +8153,7 @@
         <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O40" t="n">
         <v>1.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -757,52 +757,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
         <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>10.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
@@ -811,7 +811,7 @@
         <v>6.8</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
         <v>25</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -847,80 +847,80 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK2" t="n">
         <v>17.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AL3" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>150</v>
+        <v>590</v>
       </c>
       <c r="AO3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
         <v>5.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1145,85 +1145,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
         <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1232,83 +1232,83 @@
         <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC4" t="n">
         <v>21</v>
       </c>
-      <c r="BB4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
         <v>5.1</v>
@@ -1357,13 +1357,13 @@
         <v>7.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
@@ -1372,7 +1372,7 @@
         <v>2.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.62</v>
@@ -1381,7 +1381,7 @@
         <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>1.89</v>
@@ -1390,7 +1390,7 @@
         <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.8</v>
@@ -1471,13 +1471,13 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.65</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.66</v>
-      </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1578,31 +1578,31 @@
         <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
         <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1614,10 +1614,10 @@
         <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
@@ -1626,37 +1626,37 @@
         <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS6" t="n">
         <v>75</v>
       </c>
-      <c r="AP6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>29</v>
-      </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
         <v>20</v>
@@ -1671,7 +1671,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
         <v>55</v>
@@ -1680,7 +1680,7 @@
         <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>26</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1733,34 +1733,34 @@
         <v>1.54</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R7" t="n">
         <v>1.51</v>
@@ -1769,10 +1769,10 @@
         <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1835,10 +1835,10 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
         <v>4.2</v>
@@ -1850,7 +1850,7 @@
         <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="AV7" t="n">
         <v>4.2</v>
@@ -1859,38 +1859,38 @@
         <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BA7" t="n">
         <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
         <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH8" t="n">
         <v>19</v>
       </c>
-      <c r="AF8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
       <c r="AI8" t="n">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA8" t="n">
         <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2115,118 +2115,118 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.33</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.34</v>
-      </c>
       <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
         <v>4.2</v>
@@ -2235,25 +2235,25 @@
         <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
         <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="BA9" t="n">
         <v>4.2</v>
@@ -2262,23 +2262,23 @@
         <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
         <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2330,31 +2330,31 @@
         <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.28</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.24</v>
@@ -2363,10 +2363,10 @@
         <v>2.2</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
         <v>42</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
@@ -2387,25 +2387,25 @@
         <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
@@ -2417,19 +2417,19 @@
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2450,7 +2450,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>13</v>
@@ -2459,20 +2459,20 @@
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD11" t="n">
         <v>500</v>
       </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>16</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AV11" t="n">
         <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2697,88 +2697,88 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
         <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13</v>
-      </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2802,34 +2802,34 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>5.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AR12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX12" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.7</v>
       </c>
       <c r="AY12" t="n">
         <v>6</v>
@@ -2838,29 +2838,29 @@
         <v>5.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
         <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
         <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2954,7 +2954,7 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>1000</v>
@@ -2963,10 +2963,10 @@
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>1000</v>
@@ -3023,7 +3023,7 @@
         <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
@@ -3032,19 +3032,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
         <v>15</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I14" t="n">
         <v>2.98</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3115,10 +3115,10 @@
         <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
@@ -3133,37 +3133,37 @@
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AG14" t="n">
         <v>1000</v>
@@ -3172,10 +3172,10 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3187,7 +3187,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3202,10 +3202,10 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
@@ -3214,10 +3214,10 @@
         <v>7.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -3226,29 +3226,29 @@
         <v>10.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF14" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
         <v>1.58</v>
@@ -3291,28 +3291,28 @@
         <v>10.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
         <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -3321,7 +3321,7 @@
         <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
         <v>1.72</v>
@@ -3330,7 +3330,7 @@
         <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X15" t="n">
         <v>90</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
         <v>15</v>
@@ -3357,10 +3357,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AY15" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
         <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
         <v>1.92</v>
@@ -3527,10 +3527,10 @@
         <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>42</v>
@@ -3551,7 +3551,7 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -3563,7 +3563,7 @@
         <v>110</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>26</v>
@@ -3575,22 +3575,22 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
         <v>9.6</v>
@@ -3614,29 +3614,29 @@
         <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>18.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>100</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
         <v>1.82</v>
@@ -3676,13 +3676,13 @@
         <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.55</v>
@@ -3694,7 +3694,7 @@
         <v>2.96</v>
       </c>
       <c r="O17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P17" t="n">
         <v>1.64</v>
@@ -3733,7 +3733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC17" t="n">
         <v>8.6</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3784,7 +3784,7 @@
         <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
         <v>5.8</v>
@@ -3796,7 +3796,7 @@
         <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>8.4</v>
@@ -3808,7 +3808,7 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
@@ -3817,20 +3817,20 @@
         <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>13</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3864,28 +3864,28 @@
         <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
@@ -3900,13 +3900,13 @@
         <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
@@ -3918,7 +3918,7 @@
         <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3972,37 +3972,37 @@
         <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
         <v>8.4</v>
@@ -4011,20 +4011,20 @@
         <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.98</v>
@@ -4073,19 +4073,19 @@
         <v>3.25</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
         <v>1.52</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
         <v>2.6</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>17.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -4184,7 +4184,7 @@
         <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -4199,13 +4199,13 @@
         <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE19" t="n">
         <v>11</v>
@@ -4214,11 +4214,11 @@
         <v>9.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G20" t="n">
         <v>1.88</v>
@@ -4279,7 +4279,7 @@
         <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
         <v>2.2</v>
@@ -4297,7 +4297,7 @@
         <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
         <v>1.92</v>
@@ -4321,7 +4321,7 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4333,7 +4333,7 @@
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4363,10 +4363,10 @@
         <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>6.4</v>
@@ -4378,7 +4378,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>8.800000000000001</v>
@@ -4390,29 +4390,29 @@
         <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC20" t="n">
         <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>1.89</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -4470,7 +4470,7 @@
         <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
         <v>1.74</v>
@@ -4482,19 +4482,19 @@
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X21" t="n">
         <v>20</v>
@@ -4512,10 +4512,10 @@
         <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4524,7 +4524,7 @@
         <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
         <v>1000</v>
@@ -4551,28 +4551,28 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
         <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
@@ -4581,32 +4581,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
       </c>
       <c r="BE21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.22</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4676,22 +4676,22 @@
         <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
         <v>22</v>
@@ -4703,13 +4703,13 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4721,10 +4721,10 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>75</v>
@@ -4733,7 +4733,7 @@
         <v>65</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4742,7 +4742,7 @@
         <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
         <v>11.5</v>
@@ -4763,10 +4763,10 @@
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
@@ -4778,7 +4778,7 @@
         <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>24</v>
@@ -4787,20 +4787,20 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>1.47</v>
@@ -4855,34 +4855,34 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
         <v>19.5</v>
@@ -4891,7 +4891,7 @@
         <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4906,7 +4906,7 @@
         <v>34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF23" t="n">
         <v>24</v>
@@ -4915,7 +4915,7 @@
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4942,7 +4942,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>23</v>
@@ -4951,7 +4951,7 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4960,10 +4960,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
         <v>9</v>
@@ -4978,23 +4978,23 @@
         <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H24" t="n">
         <v>2.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -5046,7 +5046,7 @@
         <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
         <v>3.7</v>
@@ -5055,7 +5055,7 @@
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
@@ -5076,7 +5076,7 @@
         <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X24" t="n">
         <v>15.5</v>
@@ -5127,10 +5127,10 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT24" t="n">
         <v>9.800000000000001</v>
@@ -5163,13 +5163,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BC24" t="n">
         <v>14.5</v>
@@ -5178,17 +5178,17 @@
         <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.38</v>
@@ -5264,19 +5264,19 @@
         <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
         <v>1.07</v>
       </c>
       <c r="W25" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="X25" t="n">
         <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5288,10 +5288,10 @@
         <v>7.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5303,7 +5303,7 @@
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5330,13 +5330,13 @@
         <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
         <v>6.6</v>
@@ -5345,10 +5345,10 @@
         <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
         <v>6.4</v>
@@ -5357,13 +5357,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
@@ -5372,17 +5372,17 @@
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG25" t="n">
         <v>15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H26" t="n">
         <v>3.1</v>
@@ -5425,10 +5425,10 @@
         <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L26" t="n">
         <v>1.56</v>
@@ -5440,16 +5440,16 @@
         <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
         <v>4.8</v>
@@ -5458,7 +5458,7 @@
         <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
         <v>1.42</v>
@@ -5473,13 +5473,13 @@
         <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
@@ -5503,46 +5503,46 @@
         <v>160</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="n">
         <v>60</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5551,32 +5551,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
         <v>30</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BD26" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BE26" t="n">
         <v>12.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>1.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
         <v>5.8</v>
@@ -5631,13 +5631,13 @@
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
         <v>2.14</v>
@@ -5649,55 +5649,55 @@
         <v>3.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V27" t="n">
         <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB27" t="n">
         <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG27" t="n">
         <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5712,22 +5712,22 @@
         <v>14.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>410</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS27" t="n">
         <v>29</v>
       </c>
-      <c r="AS27" t="n">
-        <v>44</v>
-      </c>
       <c r="AT27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
@@ -5736,41 +5736,41 @@
         <v>18.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB27" t="n">
         <v>17.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>17.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF27" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H28" t="n">
         <v>6.6</v>
@@ -5828,10 +5828,10 @@
         <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.74</v>
@@ -5855,19 +5855,19 @@
         <v>2.74</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
         <v>70</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
         <v>19</v>
@@ -5879,10 +5879,10 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5891,10 +5891,10 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
         <v>1000</v>
@@ -5903,68 +5903,68 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AY28" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB28" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC28" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
         <v>18</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
         <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5998,67 +5998,67 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H29" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="I29" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R29" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="U29" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB29" t="n">
         <v>1000</v>
@@ -6082,7 +6082,7 @@
         <v>500</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA29" t="n">
         <v>15</v>
       </c>
-      <c r="BA29" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC29" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="G30" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H30" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF30" t="n">
         <v>9</v>
       </c>
-      <c r="Z30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>3</v>
-      </c>
       <c r="BG30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>
@@ -6395,10 +6395,10 @@
         <v>4.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.62</v>
@@ -6410,7 +6410,7 @@
         <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P31" t="n">
         <v>1.53</v>
@@ -6419,13 +6419,13 @@
         <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U31" t="n">
         <v>1.71</v>
@@ -6434,7 +6434,7 @@
         <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="X31" t="n">
         <v>10</v>
@@ -6449,34 +6449,34 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>13</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AJ31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK31" t="n">
         <v>32</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>65</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -6485,10 +6485,10 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
         <v>7.4</v>
@@ -6497,56 +6497,56 @@
         <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB31" t="n">
         <v>13</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD31" t="n">
         <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
         <v>23</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6577,70 +6577,70 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H32" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I32" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
         <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U32" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB32" t="n">
         <v>9</v>
@@ -6652,10 +6652,10 @@
         <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
         <v>11.5</v>
@@ -6664,83 +6664,83 @@
         <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE32" t="n">
         <v>28</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF32" t="n">
         <v>19</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
         <v>3.35</v>
@@ -6795,16 +6795,16 @@
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>1.52</v>
       </c>
       <c r="P33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
         <v>1.2</v>
@@ -6885,7 +6885,7 @@
         <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS33" t="n">
         <v>10</v>
@@ -6900,7 +6900,7 @@
         <v>7</v>
       </c>
       <c r="AW33" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AX33" t="n">
         <v>5.6</v>
@@ -6912,7 +6912,7 @@
         <v>7.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BB33" t="n">
         <v>7.6</v>
@@ -6921,20 +6921,20 @@
         <v>7.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="BF33" t="n">
         <v>5.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G34" t="n">
         <v>3.15</v>
@@ -6977,10 +6977,10 @@
         <v>2.98</v>
       </c>
       <c r="J34" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L34" t="n">
         <v>1.52</v>
@@ -6992,7 +6992,7 @@
         <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P34" t="n">
         <v>1.64</v>
@@ -7010,19 +7010,19 @@
         <v>1.89</v>
       </c>
       <c r="U34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V34" t="n">
         <v>1.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X34" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y34" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
@@ -7049,7 +7049,7 @@
         <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
@@ -7076,59 +7076,59 @@
         <v>4.9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AT34" t="n">
         <v>4.9</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.52</v>
+        <v>18</v>
       </c>
       <c r="AX34" t="n">
         <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="BB34" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="BF34" t="n">
         <v>7.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.82</v>
+        <v>10</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7162,10 +7162,10 @@
         <v>1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H35" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
         <v>7</v>
@@ -7192,19 +7192,19 @@
         <v>1.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T35" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U35" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V35" t="n">
         <v>1.17</v>
@@ -7213,7 +7213,7 @@
         <v>2.24</v>
       </c>
       <c r="X35" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
@@ -7270,13 +7270,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="AT35" t="n">
         <v>4.4</v>
@@ -7285,10 +7285,10 @@
         <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AX35" t="n">
         <v>5.1</v>
@@ -7297,32 +7297,32 @@
         <v>7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BB35" t="n">
         <v>8.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE35" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G36" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H36" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I36" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J36" t="n">
         <v>3.2</v>
@@ -7371,22 +7371,22 @@
         <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M36" t="n">
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O36" t="n">
         <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R36" t="n">
         <v>1.21</v>
@@ -7401,10 +7401,10 @@
         <v>1.83</v>
       </c>
       <c r="V36" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
         <v>12</v>
@@ -7413,25 +7413,25 @@
         <v>7.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AA36" t="n">
         <v>44</v>
       </c>
       <c r="AB36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
         <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG36" t="n">
         <v>18</v>
@@ -7446,7 +7446,7 @@
         <v>90</v>
       </c>
       <c r="AK36" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL36" t="n">
         <v>90</v>
@@ -7473,7 +7473,7 @@
         <v>14.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU36" t="n">
         <v>6.8</v>
@@ -7482,41 +7482,41 @@
         <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC36" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BG36" t="n">
         <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R37" t="n">
         <v>1.35</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="G38" t="n">
         <v>6.6</v>
@@ -7759,7 +7759,7 @@
         <v>3.85</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
@@ -7768,7 +7768,7 @@
         <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P38" t="n">
         <v>1.69</v>
@@ -7777,7 +7777,7 @@
         <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -7789,7 +7789,7 @@
         <v>1.82</v>
       </c>
       <c r="V38" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W38" t="n">
         <v>1.19</v>
@@ -7804,7 +7804,7 @@
         <v>12</v>
       </c>
       <c r="AA38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB38" t="n">
         <v>20</v>
@@ -7816,7 +7816,7 @@
         <v>12.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF38" t="n">
         <v>55</v>
@@ -7861,50 +7861,50 @@
         <v>16.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW38" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA38" t="n">
         <v>4.7</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG38" t="n">
         <v>13</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
         <v>3.35</v>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M39" t="n">
         <v>1.11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G40" t="n">
         <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I40" t="n">
         <v>4.8</v>
@@ -8162,13 +8162,13 @@
         <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R40" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T40" t="n">
         <v>2.06</v>
@@ -8189,7 +8189,7 @@
         <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
@@ -8237,7 +8237,7 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ40" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
         <v>7</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -8258,7 +8258,7 @@
         <v>6</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX40" t="n">
         <v>9.800000000000001</v>
@@ -8276,7 +8276,7 @@
         <v>6.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD40" t="n">
         <v>7.6</v>
@@ -8288,11 +8288,11 @@
         <v>18</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,61 +757,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>9.6</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.42</v>
+        <v>9.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,92 +835,92 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>1.84</v>
       </c>
       <c r="AG2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
         <v>16</v>
       </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10</v>
       </c>
-      <c r="AU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BG2" t="n">
         <v>12.5</v>
       </c>
-      <c r="BD2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>190</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V3" t="n">
+        <v>26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV3" t="n">
         <v>7.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AW3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>30</v>
       </c>
-      <c r="AC3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>660</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>370</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>370</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>470</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>200</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>210</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
@@ -1169,7 +1169,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
@@ -1178,13 +1178,13 @@
         <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
@@ -1193,22 +1193,22 @@
         <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
         <v>13.5</v>
@@ -1220,7 +1220,7 @@
         <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1232,7 +1232,7 @@
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
@@ -1241,7 +1241,7 @@
         <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1250,7 +1250,7 @@
         <v>15.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1304,11 +1304,11 @@
         <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
         <v>8.4</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
@@ -1366,22 +1366,22 @@
         <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>1.9</v>
@@ -1390,7 +1390,7 @@
         <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
         <v>42</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
         <v>36</v>
@@ -1441,19 +1441,19 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
@@ -1465,19 +1465,19 @@
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1489,27 +1489,27 @@
         <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>2.86</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB6" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="BC6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF6" t="n">
         <v>24</v>
       </c>
-      <c r="Z6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
       <c r="BG6" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NK Brinje Grosuplje</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>1.34</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.7</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>3.85</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>780</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="n">
         <v>11</v>
       </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>300</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AS7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY7" t="n">
         <v>11</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AZ7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BA7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.45</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.14</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL8" t="n">
         <v>27</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS8" t="n">
         <v>55</v>
       </c>
-      <c r="AP8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Peruvian Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union Comercio</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA9" t="n">
         <v>7.2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="BB9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF9" t="n">
         <v>15</v>
       </c>
-      <c r="Z9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>27</v>
-      </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thisted</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Union Comercio</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>1.64</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>2.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y10" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>15.5</v>
       </c>
       <c r="AB10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT10" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU10" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fremad Amager</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
         <v>3.75</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>640</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>95</v>
-      </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
         <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>15</v>
       </c>
-      <c r="BA11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>16</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Roskilde</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AA12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" t="n">
         <v>75</v>
       </c>
-      <c r="AB12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>40</v>
-      </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>26</v>
       </c>
-      <c r="AX12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>18</v>
-      </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Fleury Merogis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.94</v>
+        <v>1.97</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>11</v>
       </c>
-      <c r="Y13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AW13" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>17.5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.59</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB14" t="n">
         <v>9.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AQ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
         <v>34</v>
       </c>
-      <c r="AL14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB14" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BC14" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aubagne FC</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>2.96</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
         <v>13</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR15" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
         <v>38</v>
       </c>
-      <c r="AE15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="BB15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE15" t="n">
         <v>11</v>
       </c>
-      <c r="AG15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="BF15" t="n">
         <v>17.5</v>
       </c>
-      <c r="AW15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Versailles 78 FC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="X16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP16" t="n">
         <v>11</v>
       </c>
-      <c r="Y16" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AQ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR16" t="n">
         <v>26</v>
       </c>
-      <c r="AE16" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>450</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="AS16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU16" t="n">
         <v>9</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AV16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS16" t="n">
+      <c r="AX16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BF16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Villefranche Beaujolais</t>
+          <t>Versailles 78 FC</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3673,164 +3673,164 @@
         <v>1.73</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.95</v>
       </c>
-      <c r="K17" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC17" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
         <v>10.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
         <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.86</v>
+        <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>470</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AH18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16</v>
-      </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF18" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fleury Merogis</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche Beaujolais</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
         <v>1.92</v>
       </c>
       <c r="U19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC19" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="BD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG19" t="n">
         <v>12</v>
       </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.82</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -4261,10 +4261,10 @@
         <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.49</v>
@@ -4273,13 +4273,13 @@
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
         <v>2.24</v>
@@ -4294,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
         <v>1.18</v>
@@ -4360,10 +4360,10 @@
         <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
         <v>11</v>
@@ -4375,7 +4375,7 @@
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
         <v>10.5</v>
@@ -4405,21 +4405,21 @@
         <v>11</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
         <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>3.75</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
         <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="n">
         <v>42</v>
       </c>
-      <c r="AL21" t="n">
-        <v>85</v>
-      </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF21" t="n">
         <v>13</v>
       </c>
-      <c r="AW21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>16</v>
-      </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>5.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>1.54</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>1.56</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>2.74</v>
       </c>
       <c r="W22" t="n">
-        <v>1.96</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE22" t="n">
         <v>15</v>
       </c>
-      <c r="Z22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>120</v>
-      </c>
       <c r="AF22" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AH22" t="n">
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AS22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="AX22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY22" t="n">
         <v>15</v>
       </c>
-      <c r="AW22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC22" t="n">
         <v>10</v>
       </c>
-      <c r="AY22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="G23" t="n">
-        <v>2.84</v>
+        <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.72</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL23" t="n">
         <v>500</v>
       </c>
-      <c r="AB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AW23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>13</v>
       </c>
-      <c r="AH23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="BA23" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="BB23" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.33</v>
+        <v>2.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="H24" t="n">
-        <v>12.5</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>3.75</v>
+        <v>1.61</v>
       </c>
       <c r="X24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z24" t="n">
         <v>21</v>
       </c>
-      <c r="Y24" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
       </c>
       <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
         <v>60</v>
       </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO24" t="n">
         <v>55</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="AW24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BD24" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>70</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BG24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="T25" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AR25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC25" t="n">
         <v>16</v>
       </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK25" t="n">
+      <c r="BD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG25" t="n">
         <v>36</v>
       </c>
-      <c r="AL25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>12</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.84</v>
+        <v>2.82</v>
       </c>
       <c r="G26" t="n">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="W26" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="X26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB26" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN26" t="n">
+      <c r="BC26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>34</v>
-      </c>
       <c r="BE26" t="n">
-        <v>80</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>1.97</v>
       </c>
       <c r="G27" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
         <v>8</v>
       </c>
-      <c r="J27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X27" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AD27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL27" t="n">
         <v>70</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO27" t="n">
         <v>500</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AY27" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.2</v>
+        <v>1.37</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>1.56</v>
+        <v>11</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="K28" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.3</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.59</v>
-      </c>
       <c r="U28" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="V28" t="n">
-        <v>2.66</v>
+        <v>1.09</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>3.55</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AD28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>25</v>
       </c>
-      <c r="AB28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AR28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AV28" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="I29" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
@@ -6022,40 +6022,40 @@
         <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U29" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V29" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="W29" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
         <v>20</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AD29" t="n">
         <v>36</v>
@@ -6076,7 +6076,7 @@
         <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
@@ -6091,7 +6091,7 @@
         <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6100,72 +6100,72 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>85</v>
+        <v>19.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT29" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AX29" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AY29" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BC29" t="n">
-        <v>32</v>
+        <v>2.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q30" t="n">
         <v>2.16</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.84</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="U30" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK30" t="n">
         <v>29</v>
       </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AL30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT30" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6</v>
-      </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BB30" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG30" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H31" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="R31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>1.83</v>
       </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.77</v>
-      </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA31" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG31" t="n">
         <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI31" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL31" t="n">
-        <v>46</v>
+        <v>460</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AO31" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY31" t="n">
         <v>10</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="BB31" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF31" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="H32" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.58</v>
@@ -6601,40 +6601,40 @@
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O32" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P32" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="X32" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Z32" t="n">
         <v>1000</v>
@@ -6643,25 +6643,25 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC32" t="n">
         <v>13</v>
       </c>
-      <c r="AC32" t="n">
-        <v>15</v>
-      </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AG32" t="n">
         <v>36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6670,7 +6670,7 @@
         <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
@@ -6679,25 +6679,25 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR32" t="n">
         <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AU32" t="n">
         <v>5.7</v>
@@ -6706,19 +6706,19 @@
         <v>10.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ32" t="n">
         <v>13</v>
       </c>
       <c r="BA32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6730,17 +6730,17 @@
         <v>10.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.84</v>
+        <v>3.95</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G33" t="n">
         <v>2.84</v>
       </c>
-      <c r="G33" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H33" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="I33" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>2.96</v>
       </c>
       <c r="K33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L33" t="n">
         <v>1.5</v>
@@ -6819,13 +6819,13 @@
         <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X33" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
@@ -6840,7 +6840,7 @@
         <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
@@ -6849,13 +6849,13 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
         <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6885,10 +6885,10 @@
         <v>5.1</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AS33" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT33" t="n">
         <v>4.9</v>
@@ -6897,34 +6897,34 @@
         <v>4.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW33" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AX33" t="n">
         <v>7.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="BB33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD33" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC33" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE33" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BF33" t="n">
         <v>7.2</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.67</v>
       </c>
       <c r="G34" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I34" t="n">
         <v>6.6</v>
@@ -6995,25 +6995,25 @@
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V34" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W34" t="n">
         <v>2.28</v>
@@ -7082,7 +7082,7 @@
         <v>7.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT34" t="n">
         <v>6.4</v>
@@ -7091,7 +7091,7 @@
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AW34" t="n">
         <v>8.199999999999999</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BA34" t="n">
         <v>8.199999999999999</v>
@@ -7112,7 +7112,7 @@
         <v>8.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD34" t="n">
         <v>7.4</v>
@@ -7124,11 +7124,11 @@
         <v>5.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G35" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H35" t="n">
         <v>2.32</v>
       </c>
       <c r="I35" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L35" t="n">
         <v>1.53</v>
@@ -7183,64 +7183,64 @@
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P35" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T35" t="n">
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V35" t="n">
         <v>1.7</v>
       </c>
       <c r="W35" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
         <v>100</v>
       </c>
       <c r="AB35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
         <v>65</v>
       </c>
       <c r="AF35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG35" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH35" t="n">
         <v>21</v>
@@ -7249,40 +7249,40 @@
         <v>370</v>
       </c>
       <c r="AJ35" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AK35" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AL35" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO35" t="n">
         <v>75</v>
       </c>
       <c r="AP35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR35" t="n">
         <v>12.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
         <v>10</v>
@@ -7291,38 +7291,38 @@
         <v>15</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BB35" t="n">
         <v>12.5</v>
       </c>
       <c r="BC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD35" t="n">
         <v>12</v>
       </c>
-      <c r="BD35" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BE35" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG35" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>2.56</v>
       </c>
       <c r="G36" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H36" t="n">
         <v>2.86</v>
@@ -7365,7 +7365,7 @@
         <v>3.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K36" t="n">
         <v>3.55</v>
@@ -7392,7 +7392,7 @@
         <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T36" t="n">
         <v>1.84</v>
@@ -7401,7 +7401,7 @@
         <v>1.98</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
         <v>1.54</v>
@@ -7437,7 +7437,7 @@
         <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7467,10 +7467,10 @@
         <v>6.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="AT36" t="n">
         <v>6.2</v>
@@ -7482,7 +7482,7 @@
         <v>7.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AX36" t="n">
         <v>9</v>
@@ -7494,29 +7494,29 @@
         <v>10.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.04</v>
+        <v>7.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC36" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="BF36" t="n">
         <v>7.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="I37" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.43</v>
@@ -7571,67 +7571,67 @@
         <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O37" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P37" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
         <v>1.94</v>
       </c>
       <c r="U37" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V37" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="W37" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X37" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC37" t="n">
         <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG37" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AH37" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI37" t="n">
         <v>50</v>
@@ -7652,65 +7652,65 @@
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>6.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV37" t="n">
         <v>8.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>18.5</v>
       </c>
-      <c r="AZ37" t="n">
-        <v>18</v>
-      </c>
       <c r="BA37" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
@@ -7741,49 +7741,49 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="G38" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H38" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
       <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
         <v>3.15</v>
       </c>
-      <c r="K38" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L38" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O38" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>1.87</v>
@@ -7792,7 +7792,7 @@
         <v>1.34</v>
       </c>
       <c r="W38" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X38" t="n">
         <v>11.5</v>
@@ -7852,7 +7852,7 @@
         <v>3.65</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR38" t="n">
         <v>4.5</v>
@@ -7861,25 +7861,25 @@
         <v>5.1</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AU38" t="n">
         <v>3.25</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AW38" t="n">
         <v>4.9</v>
       </c>
       <c r="AX38" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BA38" t="n">
         <v>5</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 09:47:03</t>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,184 +7921,378 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22:10:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>C J Antoniana</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="G39" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="H39" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>380</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22:10:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J40" t="n">
         <v>3.3</v>
       </c>
-      <c r="L39" t="n">
+      <c r="K40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L40" t="n">
         <v>1.55</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R39" t="n">
+      <c r="M40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.22</v>
       </c>
-      <c r="S39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF40" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG39" t="n">
+      <c r="AG40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ40" t="n">
         <v>12</v>
       </c>
-      <c r="AH39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AR40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT40" t="n">
         <v>6</v>
       </c>
-      <c r="AU39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ39" t="n">
+      <c r="AU40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV40" t="n">
         <v>19</v>
       </c>
-      <c r="BA39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-03-27 09:47:03</t>
+      <c r="AW40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-27 12:02:41</t>
         </is>
       </c>
     </row>
